--- a/research/traditional_assets/database/data/pakistan/pakistan_tobacco.xlsx
+++ b/research/traditional_assets/database/data/pakistan/pakistan_tobacco.xlsx
@@ -1537,7 +1537,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1674,22 +1674,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1369198098774121</v>
+        <v>0.1365546924287677</v>
       </c>
       <c r="C2">
-        <v>1240.885976899568</v>
+        <v>1233.433730356749</v>
       </c>
       <c r="D2">
-        <v>1219.885976899568</v>
+        <v>1224.793730356749</v>
       </c>
       <c r="E2">
-        <v>-14.1</v>
+        <v>-1.74</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>12.36</v>
       </c>
       <c r="G2">
         <v>21</v>
@@ -1710,28 +1710,28 @@
         <v>153.3</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.6217079999999999</v>
       </c>
       <c r="N2">
-        <v>153.3</v>
+        <v>152.678292</v>
       </c>
       <c r="O2">
-        <v>44.457</v>
+        <v>44.27670467999999</v>
       </c>
       <c r="P2">
-        <v>108.843</v>
+        <v>108.40158732</v>
       </c>
       <c r="Q2">
-        <v>114.143</v>
+        <v>113.70158732</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1369198098774121</v>
+        <v>0.1375732953825936</v>
       </c>
       <c r="T2">
-        <v>0.5572774141861078</v>
+        <v>0.5612740501868364</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1748,7 +1748,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>246.5787797486923</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1756,22 +1756,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1365546924287677</v>
+        <v>0.1361895749801232</v>
       </c>
       <c r="C3">
-        <v>1233.433730356749</v>
+        <v>1226.021132333603</v>
       </c>
       <c r="D3">
-        <v>1224.793730356749</v>
+        <v>1229.741132333603</v>
       </c>
       <c r="E3">
-        <v>-1.74</v>
+        <v>10.62</v>
       </c>
       <c r="F3">
-        <v>12.36</v>
+        <v>24.72</v>
       </c>
       <c r="G3">
         <v>21</v>
@@ -1792,28 +1792,28 @@
         <v>153.3</v>
       </c>
       <c r="M3">
-        <v>0.6217079999999999</v>
+        <v>1.243416</v>
       </c>
       <c r="N3">
-        <v>152.678292</v>
+        <v>152.056584</v>
       </c>
       <c r="O3">
-        <v>44.27670467999999</v>
+        <v>44.09640936</v>
       </c>
       <c r="P3">
-        <v>108.40158732</v>
+        <v>107.96017464</v>
       </c>
       <c r="Q3">
-        <v>113.70158732</v>
+        <v>113.26017464</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1375732953825936</v>
+        <v>0.1382401173266563</v>
       </c>
       <c r="T3">
-        <v>0.5612740501868364</v>
+        <v>0.56535225018758</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1830,7 +1830,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>246.5787797486923</v>
+        <v>123.2893898743462</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1838,22 +1838,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1361895749801232</v>
+        <v>0.1358244575314787</v>
       </c>
       <c r="C4">
-        <v>1226.021132333603</v>
+        <v>1218.648665244578</v>
       </c>
       <c r="D4">
-        <v>1229.741132333603</v>
+        <v>1234.728665244578</v>
       </c>
       <c r="E4">
-        <v>10.62</v>
+        <v>22.98</v>
       </c>
       <c r="F4">
-        <v>24.72</v>
+        <v>37.08</v>
       </c>
       <c r="G4">
         <v>21</v>
@@ -1874,28 +1874,28 @@
         <v>153.3</v>
       </c>
       <c r="M4">
-        <v>1.243416</v>
+        <v>1.865124</v>
       </c>
       <c r="N4">
-        <v>152.056584</v>
+        <v>151.434876</v>
       </c>
       <c r="O4">
-        <v>44.09640936</v>
+        <v>43.91611404</v>
       </c>
       <c r="P4">
-        <v>107.96017464</v>
+        <v>107.51876196</v>
       </c>
       <c r="Q4">
-        <v>113.26017464</v>
+        <v>112.81876196</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1382401173266563</v>
+        <v>0.1389206881767821</v>
       </c>
       <c r="T4">
-        <v>0.56535225018758</v>
+        <v>0.5695145367862769</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1912,7 +1912,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>123.2893898743462</v>
+        <v>82.19292658289744</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1920,22 +1920,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1358244575314787</v>
+        <v>0.1354593400828342</v>
       </c>
       <c r="C5">
-        <v>1218.648665244578</v>
+        <v>1211.316819362217</v>
       </c>
       <c r="D5">
-        <v>1234.728665244578</v>
+        <v>1239.756819362217</v>
       </c>
       <c r="E5">
-        <v>22.98</v>
+        <v>35.34</v>
       </c>
       <c r="F5">
-        <v>37.08</v>
+        <v>49.44</v>
       </c>
       <c r="G5">
         <v>21</v>
@@ -1956,28 +1956,28 @@
         <v>153.3</v>
       </c>
       <c r="M5">
-        <v>1.865124</v>
+        <v>2.486832</v>
       </c>
       <c r="N5">
-        <v>151.434876</v>
+        <v>150.813168</v>
       </c>
       <c r="O5">
-        <v>43.91611404</v>
+        <v>43.73581872</v>
       </c>
       <c r="P5">
-        <v>107.51876196</v>
+        <v>107.07734928</v>
       </c>
       <c r="Q5">
-        <v>112.81876196</v>
+        <v>112.37734928</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1389206881767821</v>
+        <v>0.1396154375862856</v>
       </c>
       <c r="T5">
-        <v>0.5695145367862769</v>
+        <v>0.5737635376891135</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1994,7 +1994,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>82.19292658289744</v>
+        <v>61.64469493717309</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -2002,22 +2002,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1354593400828342</v>
+        <v>0.1350942226341897</v>
       </c>
       <c r="C6">
-        <v>1211.316819362217</v>
+        <v>1204.026092977819</v>
       </c>
       <c r="D6">
-        <v>1239.756819362217</v>
+        <v>1244.826092977819</v>
       </c>
       <c r="E6">
-        <v>35.34</v>
+        <v>47.7</v>
       </c>
       <c r="F6">
-        <v>49.44</v>
+        <v>61.8</v>
       </c>
       <c r="G6">
         <v>21</v>
@@ -2038,28 +2038,28 @@
         <v>153.3</v>
       </c>
       <c r="M6">
-        <v>2.486832</v>
+        <v>3.10854</v>
       </c>
       <c r="N6">
-        <v>150.813168</v>
+        <v>150.19146</v>
       </c>
       <c r="O6">
-        <v>43.73581872</v>
+        <v>43.5555234</v>
       </c>
       <c r="P6">
-        <v>107.07734928</v>
+        <v>106.6359366</v>
       </c>
       <c r="Q6">
-        <v>112.37734928</v>
+        <v>111.9359366</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1396154375862856</v>
+        <v>0.140324813299147</v>
       </c>
       <c r="T6">
-        <v>0.5737635376891135</v>
+        <v>0.5781019912425359</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>61.64469493717309</v>
+        <v>49.31575594973847</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2084,22 +2084,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1350942226341897</v>
+        <v>0.1347291051855452</v>
       </c>
       <c r="C7">
-        <v>1204.026092977819</v>
+        <v>1196.776992566045</v>
       </c>
       <c r="D7">
-        <v>1244.826092977819</v>
+        <v>1249.936992566045</v>
       </c>
       <c r="E7">
-        <v>47.7</v>
+        <v>60.06000000000001</v>
       </c>
       <c r="F7">
-        <v>61.8</v>
+        <v>74.16000000000001</v>
       </c>
       <c r="G7">
         <v>21</v>
@@ -2120,28 +2120,28 @@
         <v>153.3</v>
       </c>
       <c r="M7">
-        <v>3.10854</v>
+        <v>3.730248</v>
       </c>
       <c r="N7">
-        <v>150.19146</v>
+        <v>149.569752</v>
       </c>
       <c r="O7">
-        <v>43.5555234</v>
+        <v>43.37522808000001</v>
       </c>
       <c r="P7">
-        <v>106.6359366</v>
+        <v>106.19452392</v>
       </c>
       <c r="Q7">
-        <v>111.9359366</v>
+        <v>111.49452392</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.140324813299147</v>
+        <v>0.1410492821122821</v>
       </c>
       <c r="T7">
-        <v>0.5781019912425359</v>
+        <v>0.5825327523183718</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>49.31575594973847</v>
+        <v>41.09646329144872</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2166,22 +2166,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1347291051855452</v>
+        <v>0.1343639877369007</v>
       </c>
       <c r="C8">
-        <v>1196.776992566045</v>
+        <v>1189.570032953611</v>
       </c>
       <c r="D8">
-        <v>1249.936992566045</v>
+        <v>1255.090032953611</v>
       </c>
       <c r="E8">
-        <v>60.06</v>
+        <v>72.42</v>
       </c>
       <c r="F8">
-        <v>74.16</v>
+        <v>86.52</v>
       </c>
       <c r="G8">
         <v>21</v>
@@ -2202,28 +2202,28 @@
         <v>153.3</v>
       </c>
       <c r="M8">
-        <v>3.730248</v>
+        <v>4.351955999999999</v>
       </c>
       <c r="N8">
-        <v>149.569752</v>
+        <v>148.948044</v>
       </c>
       <c r="O8">
-        <v>43.37522808000001</v>
+        <v>43.19493276</v>
       </c>
       <c r="P8">
-        <v>106.19452392</v>
+        <v>105.75311124</v>
       </c>
       <c r="Q8">
-        <v>111.49452392</v>
+        <v>111.05311124</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1410492821122821</v>
+        <v>0.1417893308998932</v>
       </c>
       <c r="T8">
-        <v>0.5825327523183718</v>
+        <v>0.5870587985786342</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2240,7 +2240,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>41.09646329144873</v>
+        <v>35.22553996409891</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2248,22 +2248,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1343639877369007</v>
+        <v>0.1339988702882562</v>
       </c>
       <c r="C9">
-        <v>1189.570032953611</v>
+        <v>1182.405737492155</v>
       </c>
       <c r="D9">
-        <v>1255.090032953611</v>
+        <v>1260.285737492155</v>
       </c>
       <c r="E9">
-        <v>72.42000000000002</v>
+        <v>84.78</v>
       </c>
       <c r="F9">
-        <v>86.52000000000001</v>
+        <v>98.88</v>
       </c>
       <c r="G9">
         <v>21</v>
@@ -2284,28 +2284,28 @@
         <v>153.3</v>
       </c>
       <c r="M9">
-        <v>4.351956</v>
+        <v>4.973663999999999</v>
       </c>
       <c r="N9">
-        <v>148.948044</v>
+        <v>148.326336</v>
       </c>
       <c r="O9">
-        <v>43.19493276</v>
+        <v>43.01463744</v>
       </c>
       <c r="P9">
-        <v>105.75311124</v>
+        <v>105.31169856</v>
       </c>
       <c r="Q9">
-        <v>111.05311124</v>
+        <v>110.61169856</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1417893308998932</v>
+        <v>0.1425454677046263</v>
       </c>
       <c r="T9">
-        <v>0.5870587985786342</v>
+        <v>0.5916832371489021</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2322,7 +2322,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>35.2255399640989</v>
+        <v>30.82234746858655</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2330,22 +2330,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1339988702882562</v>
+        <v>0.1336337528396117</v>
       </c>
       <c r="C10">
-        <v>1182.405737492155</v>
+        <v>1175.284638235431</v>
       </c>
       <c r="D10">
-        <v>1260.285737492155</v>
+        <v>1265.524638235431</v>
       </c>
       <c r="E10">
-        <v>84.78</v>
+        <v>97.14</v>
       </c>
       <c r="F10">
-        <v>98.88</v>
+        <v>111.24</v>
       </c>
       <c r="G10">
         <v>21</v>
@@ -2366,28 +2366,28 @@
         <v>153.3</v>
       </c>
       <c r="M10">
-        <v>4.973663999999999</v>
+        <v>5.595371999999999</v>
       </c>
       <c r="N10">
-        <v>148.326336</v>
+        <v>147.704628</v>
       </c>
       <c r="O10">
-        <v>43.01463744</v>
+        <v>42.83434212</v>
       </c>
       <c r="P10">
-        <v>105.31169856</v>
+        <v>104.87028588</v>
       </c>
       <c r="Q10">
-        <v>110.61169856</v>
+        <v>110.17028588</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1425454677046263</v>
+        <v>0.1433182229006722</v>
       </c>
       <c r="T10">
-        <v>0.5916832371489021</v>
+        <v>0.5964093117317036</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>30.82234746858655</v>
+        <v>27.39764219429915</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2412,22 +2412,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1336337528396117</v>
+        <v>0.1332686353909672</v>
       </c>
       <c r="C11">
-        <v>1175.284638235431</v>
+        <v>1168.207276120931</v>
       </c>
       <c r="D11">
-        <v>1265.524638235431</v>
+        <v>1270.807276120931</v>
       </c>
       <c r="E11">
-        <v>97.14</v>
+        <v>109.5</v>
       </c>
       <c r="F11">
-        <v>111.24</v>
+        <v>123.6</v>
       </c>
       <c r="G11">
         <v>21</v>
@@ -2448,28 +2448,28 @@
         <v>153.3</v>
       </c>
       <c r="M11">
-        <v>5.595371999999999</v>
+        <v>6.217079999999999</v>
       </c>
       <c r="N11">
-        <v>147.704628</v>
+        <v>147.08292</v>
       </c>
       <c r="O11">
-        <v>42.83434212</v>
+        <v>42.6540468</v>
       </c>
       <c r="P11">
-        <v>104.87028588</v>
+        <v>104.4288732</v>
       </c>
       <c r="Q11">
-        <v>110.17028588</v>
+        <v>109.7288732</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1433182229006722</v>
+        <v>0.144108150434408</v>
       </c>
       <c r="T11">
-        <v>0.5964093117317036</v>
+        <v>0.6012404101941229</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>27.39764219429915</v>
+        <v>24.65787797486923</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2494,22 +2494,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1332686353909672</v>
+        <v>0.1329035179423227</v>
       </c>
       <c r="C12">
-        <v>1168.207276120931</v>
+        <v>1161.174201156075</v>
       </c>
       <c r="D12">
-        <v>1270.807276120931</v>
+        <v>1276.134201156075</v>
       </c>
       <c r="E12">
-        <v>109.5</v>
+        <v>121.86</v>
       </c>
       <c r="F12">
-        <v>123.6</v>
+        <v>135.96</v>
       </c>
       <c r="G12">
         <v>21</v>
@@ -2530,28 +2530,28 @@
         <v>153.3</v>
       </c>
       <c r="M12">
-        <v>6.21708</v>
+        <v>6.838788</v>
       </c>
       <c r="N12">
-        <v>147.08292</v>
+        <v>146.461212</v>
       </c>
       <c r="O12">
-        <v>42.6540468</v>
+        <v>42.47375148</v>
       </c>
       <c r="P12">
-        <v>104.4288732</v>
+        <v>103.98746052</v>
       </c>
       <c r="Q12">
-        <v>109.7288732</v>
+        <v>109.28746052</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.144108150434408</v>
+        <v>0.1449158291486772</v>
       </c>
       <c r="T12">
-        <v>0.6012404101941229</v>
+        <v>0.6061800726669336</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>24.65787797486923</v>
+        <v>22.41625270442658</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2576,22 +2576,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1329035179423227</v>
+        <v>0.1325384004936782</v>
       </c>
       <c r="C13">
-        <v>1161.174201156075</v>
+        <v>1154.185972609113</v>
       </c>
       <c r="D13">
-        <v>1276.134201156075</v>
+        <v>1281.505972609113</v>
       </c>
       <c r="E13">
-        <v>121.86</v>
+        <v>134.22</v>
       </c>
       <c r="F13">
-        <v>135.96</v>
+        <v>148.32</v>
       </c>
       <c r="G13">
         <v>21</v>
@@ -2612,28 +2612,28 @@
         <v>153.3</v>
       </c>
       <c r="M13">
-        <v>6.838788</v>
+        <v>7.460495999999999</v>
       </c>
       <c r="N13">
-        <v>146.461212</v>
+        <v>145.839504</v>
       </c>
       <c r="O13">
-        <v>42.47375148</v>
+        <v>42.29345616</v>
       </c>
       <c r="P13">
-        <v>103.98746052</v>
+        <v>103.54604784</v>
       </c>
       <c r="Q13">
-        <v>109.28746052</v>
+        <v>108.84604784</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1449158291486772</v>
+        <v>0.1457418641973616</v>
       </c>
       <c r="T13">
-        <v>0.6061800726669336</v>
+        <v>0.6112320001959445</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>22.41625270442658</v>
+        <v>20.54823164572436</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2658,22 +2658,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1325384004936782</v>
+        <v>0.1321732830450337</v>
       </c>
       <c r="C14">
-        <v>1154.185972609113</v>
+        <v>1147.243159204854</v>
       </c>
       <c r="D14">
-        <v>1281.505972609113</v>
+        <v>1286.923159204854</v>
       </c>
       <c r="E14">
-        <v>134.22</v>
+        <v>146.58</v>
       </c>
       <c r="F14">
-        <v>148.32</v>
+        <v>160.68</v>
       </c>
       <c r="G14">
         <v>21</v>
@@ -2694,28 +2694,28 @@
         <v>153.3</v>
       </c>
       <c r="M14">
-        <v>7.460495999999999</v>
+        <v>8.082203999999999</v>
       </c>
       <c r="N14">
-        <v>145.839504</v>
+        <v>145.217796</v>
       </c>
       <c r="O14">
-        <v>42.29345616</v>
+        <v>42.11316084000001</v>
       </c>
       <c r="P14">
-        <v>103.54604784</v>
+        <v>103.10463516</v>
       </c>
       <c r="Q14">
-        <v>108.84604784</v>
+        <v>108.40463516</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1457418641973616</v>
+        <v>0.14658688855751</v>
       </c>
       <c r="T14">
-        <v>0.6112320001959445</v>
+        <v>0.6164000639899903</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2732,7 +2732,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>20.54823164572436</v>
+        <v>18.96759844220711</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2740,22 +2740,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1321732830450337</v>
+        <v>0.1318081655963892</v>
       </c>
       <c r="C15">
-        <v>1147.243159204854</v>
+        <v>1140.346339325395</v>
       </c>
       <c r="D15">
-        <v>1286.923159204854</v>
+        <v>1292.386339325395</v>
       </c>
       <c r="E15">
-        <v>146.58</v>
+        <v>158.94</v>
       </c>
       <c r="F15">
-        <v>160.68</v>
+        <v>173.04</v>
       </c>
       <c r="G15">
         <v>21</v>
@@ -2776,28 +2776,28 @@
         <v>153.3</v>
       </c>
       <c r="M15">
-        <v>8.082203999999999</v>
+        <v>8.703912000000001</v>
       </c>
       <c r="N15">
-        <v>145.217796</v>
+        <v>144.596088</v>
       </c>
       <c r="O15">
-        <v>42.11316084000001</v>
+        <v>41.93286552</v>
       </c>
       <c r="P15">
-        <v>103.10463516</v>
+        <v>102.66322248</v>
       </c>
       <c r="Q15">
-        <v>108.40463516</v>
+        <v>107.96322248</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.14658688855751</v>
+        <v>0.1474515646469642</v>
       </c>
       <c r="T15">
-        <v>0.6164000639899903</v>
+        <v>0.6216883153141299</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>18.96759844220711</v>
+        <v>17.61276998204945</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2822,22 +2822,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1318081655963892</v>
+        <v>0.1314430481477447</v>
       </c>
       <c r="C16">
-        <v>1140.346339325395</v>
+        <v>1133.496101215974</v>
       </c>
       <c r="D16">
-        <v>1292.386339325395</v>
+        <v>1297.896101215974</v>
       </c>
       <c r="E16">
-        <v>158.94</v>
+        <v>171.3</v>
       </c>
       <c r="F16">
-        <v>173.04</v>
+        <v>185.4</v>
       </c>
       <c r="G16">
         <v>21</v>
@@ -2858,28 +2858,28 @@
         <v>153.3</v>
       </c>
       <c r="M16">
-        <v>8.703912000000001</v>
+        <v>9.325620000000001</v>
       </c>
       <c r="N16">
-        <v>144.596088</v>
+        <v>143.97438</v>
       </c>
       <c r="O16">
-        <v>41.93286552</v>
+        <v>41.75257019999999</v>
       </c>
       <c r="P16">
-        <v>102.66322248</v>
+        <v>102.2218098</v>
       </c>
       <c r="Q16">
-        <v>107.96322248</v>
+        <v>107.5218098</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1474515646469642</v>
+        <v>0.1483365860561703</v>
       </c>
       <c r="T16">
-        <v>0.6216883153141299</v>
+        <v>0.6271009960811906</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>17.61276998204945</v>
+        <v>16.43858531657948</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2904,22 +2904,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1314430481477447</v>
+        <v>0.1310779306991003</v>
       </c>
       <c r="C17">
-        <v>1133.496101215974</v>
+        <v>1126.693043196117</v>
       </c>
       <c r="D17">
-        <v>1297.896101215974</v>
+        <v>1303.453043196117</v>
       </c>
       <c r="E17">
-        <v>171.3</v>
+        <v>183.66</v>
       </c>
       <c r="F17">
-        <v>185.4</v>
+        <v>197.76</v>
       </c>
       <c r="G17">
         <v>21</v>
@@ -2940,28 +2940,28 @@
         <v>153.3</v>
       </c>
       <c r="M17">
-        <v>9.325620000000001</v>
+        <v>9.947327999999999</v>
       </c>
       <c r="N17">
-        <v>143.97438</v>
+        <v>143.352672</v>
       </c>
       <c r="O17">
-        <v>41.75257019999999</v>
+        <v>41.57227488</v>
       </c>
       <c r="P17">
-        <v>102.2218098</v>
+        <v>101.78039712</v>
       </c>
       <c r="Q17">
-        <v>107.5218098</v>
+        <v>107.08039712</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1483365860561703</v>
+        <v>0.1492426794036908</v>
       </c>
       <c r="T17">
-        <v>0.6271009960811906</v>
+        <v>0.6326425501998481</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>16.43858531657948</v>
+        <v>15.41117373429327</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2986,22 +2986,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1310779306991003</v>
+        <v>0.1307128132504558</v>
       </c>
       <c r="C18">
-        <v>1126.693043196117</v>
+        <v>1119.937773876232</v>
       </c>
       <c r="D18">
-        <v>1303.453043196117</v>
+        <v>1309.057773876232</v>
       </c>
       <c r="E18">
-        <v>183.66</v>
+        <v>196.02</v>
       </c>
       <c r="F18">
-        <v>197.76</v>
+        <v>210.12</v>
       </c>
       <c r="G18">
         <v>21</v>
@@ -3022,28 +3022,28 @@
         <v>153.3</v>
       </c>
       <c r="M18">
-        <v>9.947327999999999</v>
+        <v>10.569036</v>
       </c>
       <c r="N18">
-        <v>143.352672</v>
+        <v>142.730964</v>
       </c>
       <c r="O18">
-        <v>41.57227488</v>
+        <v>41.39197956</v>
       </c>
       <c r="P18">
-        <v>101.78039712</v>
+        <v>101.33898444</v>
       </c>
       <c r="Q18">
-        <v>107.08039712</v>
+        <v>106.63898444</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1492426794036908</v>
+        <v>0.1501706063258503</v>
       </c>
       <c r="T18">
-        <v>0.6326425501998481</v>
+        <v>0.6383176357430514</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -3060,7 +3060,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>15.41117373429327</v>
+        <v>14.50463410286425</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3068,22 +3068,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1307128132504558</v>
+        <v>0.1303476958018112</v>
       </c>
       <c r="C19">
-        <v>1119.937773876232</v>
+        <v>1113.23091237981</v>
       </c>
       <c r="D19">
-        <v>1309.057773876232</v>
+        <v>1314.71091237981</v>
       </c>
       <c r="E19">
-        <v>196.02</v>
+        <v>208.38</v>
       </c>
       <c r="F19">
-        <v>210.12</v>
+        <v>222.48</v>
       </c>
       <c r="G19">
         <v>21</v>
@@ -3104,28 +3104,28 @@
         <v>153.3</v>
       </c>
       <c r="M19">
-        <v>10.569036</v>
+        <v>11.190744</v>
       </c>
       <c r="N19">
-        <v>142.730964</v>
+        <v>142.109256</v>
       </c>
       <c r="O19">
-        <v>41.39197956</v>
+        <v>41.21168424</v>
       </c>
       <c r="P19">
-        <v>101.33898444</v>
+        <v>100.89757176</v>
       </c>
       <c r="Q19">
-        <v>106.63898444</v>
+        <v>106.19757176</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1501706063258503</v>
+        <v>0.1511211656119649</v>
       </c>
       <c r="T19">
-        <v>0.6383176357430514</v>
+        <v>0.6441311380068206</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -3142,7 +3142,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>14.50463410286425</v>
+        <v>13.69882109714957</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3150,22 +3150,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1303476958018112</v>
+        <v>0.1299825783531668</v>
       </c>
       <c r="C20">
-        <v>1113.23091237981</v>
+        <v>1106.573088571412</v>
       </c>
       <c r="D20">
-        <v>1314.71091237981</v>
+        <v>1320.413088571412</v>
       </c>
       <c r="E20">
-        <v>208.38</v>
+        <v>220.74</v>
       </c>
       <c r="F20">
-        <v>222.48</v>
+        <v>234.84</v>
       </c>
       <c r="G20">
         <v>21</v>
@@ -3186,28 +3186,28 @@
         <v>153.3</v>
       </c>
       <c r="M20">
-        <v>11.190744</v>
+        <v>11.812452</v>
       </c>
       <c r="N20">
-        <v>142.109256</v>
+        <v>141.487548</v>
       </c>
       <c r="O20">
-        <v>41.21168424</v>
+        <v>41.03138892</v>
       </c>
       <c r="P20">
-        <v>100.89757176</v>
+        <v>100.45615908</v>
       </c>
       <c r="Q20">
-        <v>106.19757176</v>
+        <v>105.75615908</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1511211656119649</v>
+        <v>0.1520951954977367</v>
       </c>
       <c r="T20">
-        <v>0.6441311380068206</v>
+        <v>0.650088183536362</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>13.69882109714958</v>
+        <v>12.97783051308907</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3232,22 +3232,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1299825783531668</v>
+        <v>0.1298304609045223</v>
       </c>
       <c r="C21">
-        <v>1106.573088571412</v>
+        <v>1096.603386899283</v>
       </c>
       <c r="D21">
-        <v>1320.413088571412</v>
+        <v>1322.803386899283</v>
       </c>
       <c r="E21">
-        <v>220.74</v>
+        <v>233.1</v>
       </c>
       <c r="F21">
-        <v>234.84</v>
+        <v>247.2</v>
       </c>
       <c r="G21">
         <v>21</v>
@@ -3268,45 +3268,45 @@
         <v>153.3</v>
       </c>
       <c r="M21">
-        <v>11.812452</v>
+        <v>12.80496</v>
       </c>
       <c r="N21">
-        <v>141.487548</v>
+        <v>140.49504</v>
       </c>
       <c r="O21">
-        <v>41.03138892</v>
+        <v>40.7435616</v>
       </c>
       <c r="P21">
-        <v>100.45615908</v>
+        <v>99.75147840000002</v>
       </c>
       <c r="Q21">
-        <v>105.75615908</v>
+        <v>105.0514784</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1520951954977367</v>
+        <v>0.1530935761306528</v>
       </c>
       <c r="T21">
-        <v>0.650088183536362</v>
+        <v>0.6561941552041419</v>
       </c>
       <c r="U21">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V21">
         <v>0.29</v>
       </c>
       <c r="W21">
-        <v>0.03571299999999999</v>
+        <v>0.036778</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y21">
-        <v>12.97783051308907</v>
+        <v>11.97192337969037</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3314,22 +3314,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1298304609045223</v>
+        <v>0.1294759934558778</v>
       </c>
       <c r="C22">
-        <v>1096.603386899283</v>
+        <v>1089.847034041635</v>
       </c>
       <c r="D22">
-        <v>1322.803386899283</v>
+        <v>1328.407034041635</v>
       </c>
       <c r="E22">
-        <v>233.1</v>
+        <v>245.46</v>
       </c>
       <c r="F22">
-        <v>247.2</v>
+        <v>259.56</v>
       </c>
       <c r="G22">
         <v>21</v>
@@ -3350,28 +3350,28 @@
         <v>153.3</v>
       </c>
       <c r="M22">
-        <v>12.80496</v>
+        <v>13.445208</v>
       </c>
       <c r="N22">
-        <v>140.49504</v>
+        <v>139.854792</v>
       </c>
       <c r="O22">
-        <v>40.7435616</v>
+        <v>40.55788968</v>
       </c>
       <c r="P22">
-        <v>99.75147840000002</v>
+        <v>99.29690232000002</v>
       </c>
       <c r="Q22">
-        <v>105.0514784</v>
+        <v>104.59690232</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1530935761306528</v>
+        <v>0.1541172322226301</v>
       </c>
       <c r="T22">
-        <v>0.6561941552041419</v>
+        <v>0.6624547084331314</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3388,7 +3388,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>11.97192337969037</v>
+        <v>11.4018317901813</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3396,22 +3396,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1294759934558778</v>
+        <v>0.1291215260072333</v>
       </c>
       <c r="C23">
-        <v>1089.847034041635</v>
+        <v>1083.138359391548</v>
       </c>
       <c r="D23">
-        <v>1328.407034041635</v>
+        <v>1334.058359391548</v>
       </c>
       <c r="E23">
-        <v>245.46</v>
+        <v>257.82</v>
       </c>
       <c r="F23">
-        <v>259.56</v>
+        <v>271.92</v>
       </c>
       <c r="G23">
         <v>21</v>
@@ -3432,28 +3432,28 @@
         <v>153.3</v>
       </c>
       <c r="M23">
-        <v>13.445208</v>
+        <v>14.085456</v>
       </c>
       <c r="N23">
-        <v>139.854792</v>
+        <v>139.214544</v>
       </c>
       <c r="O23">
-        <v>40.55788968</v>
+        <v>40.37221776000001</v>
       </c>
       <c r="P23">
-        <v>99.29690232000002</v>
+        <v>98.84232624000001</v>
       </c>
       <c r="Q23">
-        <v>104.59690232</v>
+        <v>104.14232624</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1541172322226301</v>
+        <v>0.1551671359067093</v>
       </c>
       <c r="T23">
-        <v>0.6624547084331314</v>
+        <v>0.6688757886679924</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3470,7 +3470,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>11.4018317901813</v>
+        <v>10.88356670880943</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3478,22 +3478,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1291215260072333</v>
+        <v>0.1287670585585888</v>
       </c>
       <c r="C24">
-        <v>1083.138359391548</v>
+        <v>1076.477974048399</v>
       </c>
       <c r="D24">
-        <v>1334.058359391548</v>
+        <v>1339.757974048399</v>
       </c>
       <c r="E24">
-        <v>257.82</v>
+        <v>270.18</v>
       </c>
       <c r="F24">
-        <v>271.92</v>
+        <v>284.28</v>
       </c>
       <c r="G24">
         <v>21</v>
@@ -3514,28 +3514,28 @@
         <v>153.3</v>
       </c>
       <c r="M24">
-        <v>14.085456</v>
+        <v>14.725704</v>
       </c>
       <c r="N24">
-        <v>139.214544</v>
+        <v>138.574296</v>
       </c>
       <c r="O24">
-        <v>40.37221776000001</v>
+        <v>40.18654584</v>
       </c>
       <c r="P24">
-        <v>98.84232624000001</v>
+        <v>98.38775016</v>
       </c>
       <c r="Q24">
-        <v>104.14232624</v>
+        <v>103.68775016</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1551671359067093</v>
+        <v>0.1562443098163491</v>
       </c>
       <c r="T24">
-        <v>0.6688757886679924</v>
+        <v>0.6754636502076551</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3552,7 +3552,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>10.88356670880943</v>
+        <v>10.4103681562525</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3560,22 +3560,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1287670585585888</v>
+        <v>0.1284125911099443</v>
       </c>
       <c r="C25">
-        <v>1076.477974048399</v>
+        <v>1069.86649959979</v>
       </c>
       <c r="D25">
-        <v>1339.757974048399</v>
+        <v>1345.50649959979</v>
       </c>
       <c r="E25">
-        <v>270.18</v>
+        <v>282.54</v>
       </c>
       <c r="F25">
-        <v>284.28</v>
+        <v>296.64</v>
       </c>
       <c r="G25">
         <v>21</v>
@@ -3596,28 +3596,28 @@
         <v>153.3</v>
       </c>
       <c r="M25">
-        <v>14.725704</v>
+        <v>15.365952</v>
       </c>
       <c r="N25">
-        <v>138.574296</v>
+        <v>137.934048</v>
       </c>
       <c r="O25">
-        <v>40.18654584</v>
+        <v>40.00087392</v>
       </c>
       <c r="P25">
-        <v>98.38775016</v>
+        <v>97.93317408000001</v>
       </c>
       <c r="Q25">
-        <v>103.68775016</v>
+        <v>103.23317408</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1562443098163491</v>
+        <v>0.1573498304078214</v>
       </c>
       <c r="T25">
-        <v>0.6754636502076551</v>
+        <v>0.6822248765246771</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3634,7 +3634,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>10.4103681562525</v>
+        <v>9.976602816408642</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3642,22 +3642,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1284125911099443</v>
+        <v>0.1283598736612998</v>
       </c>
       <c r="C26">
-        <v>1069.86649959979</v>
+        <v>1058.365653891674</v>
       </c>
       <c r="D26">
-        <v>1345.50649959979</v>
+        <v>1346.365653891674</v>
       </c>
       <c r="E26">
-        <v>282.54</v>
+        <v>294.9</v>
       </c>
       <c r="F26">
-        <v>296.64</v>
+        <v>309</v>
       </c>
       <c r="G26">
         <v>21</v>
@@ -3678,45 +3678,45 @@
         <v>153.3</v>
       </c>
       <c r="M26">
-        <v>15.365952</v>
+        <v>16.5315</v>
       </c>
       <c r="N26">
-        <v>137.934048</v>
+        <v>136.7685</v>
       </c>
       <c r="O26">
-        <v>40.00087392</v>
+        <v>39.662865</v>
       </c>
       <c r="P26">
-        <v>97.93317408000001</v>
+        <v>97.10563500000001</v>
       </c>
       <c r="Q26">
-        <v>103.23317408</v>
+        <v>102.405635</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1573498304078214</v>
+        <v>0.1584848315483997</v>
       </c>
       <c r="T26">
-        <v>0.6822248765246771</v>
+        <v>0.6891664022101532</v>
       </c>
       <c r="U26">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V26">
         <v>0.29</v>
       </c>
       <c r="W26">
-        <v>0.036778</v>
+        <v>0.037985</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y26">
-        <v>9.976602816408644</v>
+        <v>9.273205698212504</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3724,22 +3724,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1283598736612998</v>
+        <v>0.1280174762126553</v>
       </c>
       <c r="C27">
-        <v>1058.365653891674</v>
+        <v>1051.612639000809</v>
       </c>
       <c r="D27">
-        <v>1346.365653891674</v>
+        <v>1351.972639000809</v>
       </c>
       <c r="E27">
-        <v>294.9</v>
+        <v>307.26</v>
       </c>
       <c r="F27">
-        <v>309</v>
+        <v>321.36</v>
       </c>
       <c r="G27">
         <v>21</v>
@@ -3760,28 +3760,28 @@
         <v>153.3</v>
       </c>
       <c r="M27">
-        <v>16.5315</v>
+        <v>17.19276</v>
       </c>
       <c r="N27">
-        <v>136.7685</v>
+        <v>136.10724</v>
       </c>
       <c r="O27">
-        <v>39.662865</v>
+        <v>39.4710996</v>
       </c>
       <c r="P27">
-        <v>97.10563500000001</v>
+        <v>96.63614040000002</v>
       </c>
       <c r="Q27">
-        <v>102.405635</v>
+        <v>101.9361404</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1584848315483997</v>
+        <v>0.1596505083954801</v>
       </c>
       <c r="T27">
-        <v>0.6891664022101532</v>
+        <v>0.6962955366979395</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3798,7 +3798,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>9.273205698212504</v>
+        <v>8.916543940588948</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3806,22 +3806,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1280174762126553</v>
+        <v>0.1276750787640108</v>
       </c>
       <c r="C28">
-        <v>1051.612639000809</v>
+        <v>1044.906520367633</v>
       </c>
       <c r="D28">
-        <v>1351.972639000809</v>
+        <v>1357.626520367633</v>
       </c>
       <c r="E28">
-        <v>307.26</v>
+        <v>319.62</v>
       </c>
       <c r="F28">
-        <v>321.36</v>
+        <v>333.72</v>
       </c>
       <c r="G28">
         <v>21</v>
@@ -3842,28 +3842,28 @@
         <v>153.3</v>
       </c>
       <c r="M28">
-        <v>17.19276</v>
+        <v>17.85402</v>
       </c>
       <c r="N28">
-        <v>136.10724</v>
+        <v>135.44598</v>
       </c>
       <c r="O28">
-        <v>39.4710996</v>
+        <v>39.2793342</v>
       </c>
       <c r="P28">
-        <v>96.63614040000002</v>
+        <v>96.16664580000003</v>
       </c>
       <c r="Q28">
-        <v>101.9361404</v>
+        <v>101.4666458</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1596505083954801</v>
+        <v>0.1608481215945353</v>
       </c>
       <c r="T28">
-        <v>0.6962955366979395</v>
+        <v>0.7036199899388158</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3880,7 +3880,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.916543940588948</v>
+        <v>8.586301572418986</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3888,22 +3888,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1276750787640108</v>
+        <v>0.1273326813153663</v>
       </c>
       <c r="C29">
-        <v>1044.906520367633</v>
+        <v>1038.247888816292</v>
       </c>
       <c r="D29">
-        <v>1357.626520367633</v>
+        <v>1363.327888816292</v>
       </c>
       <c r="E29">
-        <v>319.62</v>
+        <v>331.98</v>
       </c>
       <c r="F29">
-        <v>333.72</v>
+        <v>346.08</v>
       </c>
       <c r="G29">
         <v>21</v>
@@ -3924,28 +3924,28 @@
         <v>153.3</v>
       </c>
       <c r="M29">
-        <v>17.85402</v>
+        <v>18.51528</v>
       </c>
       <c r="N29">
-        <v>135.44598</v>
+        <v>134.78472</v>
       </c>
       <c r="O29">
-        <v>39.2793342</v>
+        <v>39.08756880000001</v>
       </c>
       <c r="P29">
-        <v>96.16664580000003</v>
+        <v>95.69715120000001</v>
       </c>
       <c r="Q29">
-        <v>101.4666458</v>
+        <v>100.9971512</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1608481215945353</v>
+        <v>0.1620790018268976</v>
       </c>
       <c r="T29">
-        <v>0.7036199899388158</v>
+        <v>0.7111479002141609</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3962,7 +3962,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>8.586301572418986</v>
+        <v>8.279647944832593</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3970,22 +3970,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1273326813153663</v>
+        <v>0.1269902838667218</v>
       </c>
       <c r="C30">
-        <v>1038.247888816292</v>
+        <v>1031.63734513748</v>
       </c>
       <c r="D30">
-        <v>1363.327888816292</v>
+        <v>1369.07734513748</v>
       </c>
       <c r="E30">
-        <v>331.98</v>
+        <v>344.34</v>
       </c>
       <c r="F30">
-        <v>346.08</v>
+        <v>358.4400000000001</v>
       </c>
       <c r="G30">
         <v>21</v>
@@ -4006,28 +4006,28 @@
         <v>153.3</v>
       </c>
       <c r="M30">
-        <v>18.51528</v>
+        <v>19.17654</v>
       </c>
       <c r="N30">
-        <v>134.78472</v>
+        <v>134.12346</v>
       </c>
       <c r="O30">
-        <v>39.08756880000001</v>
+        <v>38.89580340000001</v>
       </c>
       <c r="P30">
-        <v>95.69715120000001</v>
+        <v>95.22765660000002</v>
       </c>
       <c r="Q30">
-        <v>100.9971512</v>
+        <v>100.5276566</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1620790018268976</v>
+        <v>0.1633445547418617</v>
       </c>
       <c r="T30">
-        <v>0.7111479002141609</v>
+        <v>0.718887864300079</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -4044,7 +4044,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>8.279647944832593</v>
+        <v>7.994142843286641</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4052,22 +4052,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1269902838667218</v>
+        <v>0.1266478864180773</v>
       </c>
       <c r="C31">
-        <v>1031.63734513748</v>
+        <v>1025.075500299484</v>
       </c>
       <c r="D31">
-        <v>1369.07734513748</v>
+        <v>1374.875500299484</v>
       </c>
       <c r="E31">
-        <v>344.34</v>
+        <v>356.7</v>
       </c>
       <c r="F31">
-        <v>358.44</v>
+        <v>370.8</v>
       </c>
       <c r="G31">
         <v>21</v>
@@ -4088,28 +4088,28 @@
         <v>153.3</v>
       </c>
       <c r="M31">
-        <v>19.17654</v>
+        <v>19.8378</v>
       </c>
       <c r="N31">
-        <v>134.12346</v>
+        <v>133.4622</v>
       </c>
       <c r="O31">
-        <v>38.89580340000001</v>
+        <v>38.704038</v>
       </c>
       <c r="P31">
-        <v>95.22765660000002</v>
+        <v>94.758162</v>
       </c>
       <c r="Q31">
-        <v>100.5276566</v>
+        <v>100.058162</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1633445547418617</v>
+        <v>0.164646266311539</v>
       </c>
       <c r="T31">
-        <v>0.718887864300079</v>
+        <v>0.7268489702170234</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.994142843286642</v>
+        <v>7.727671415177086</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4134,22 +4134,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1266478864180773</v>
+        <v>0.1264815689694328</v>
       </c>
       <c r="C32">
-        <v>1025.075500299484</v>
+        <v>1015.549676534954</v>
       </c>
       <c r="D32">
-        <v>1374.875500299484</v>
+        <v>1377.709676534954</v>
       </c>
       <c r="E32">
-        <v>356.7</v>
+        <v>369.06</v>
       </c>
       <c r="F32">
-        <v>370.8</v>
+        <v>383.16</v>
       </c>
       <c r="G32">
         <v>21</v>
@@ -4170,45 +4170,45 @@
         <v>153.3</v>
       </c>
       <c r="M32">
-        <v>19.8378</v>
+        <v>20.805588</v>
       </c>
       <c r="N32">
-        <v>133.4622</v>
+        <v>132.494412</v>
       </c>
       <c r="O32">
-        <v>38.704038</v>
+        <v>38.42337948</v>
       </c>
       <c r="P32">
-        <v>94.758162</v>
+        <v>94.07103252000002</v>
       </c>
       <c r="Q32">
-        <v>100.058162</v>
+        <v>99.37103252</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.164646266311539</v>
+        <v>0.1659857086513519</v>
       </c>
       <c r="T32">
-        <v>0.7268489702170234</v>
+        <v>0.7350408328272126</v>
       </c>
       <c r="U32">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V32">
         <v>0.29</v>
       </c>
       <c r="W32">
-        <v>0.037985</v>
+        <v>0.038553</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y32">
-        <v>7.727671415177086</v>
+        <v>7.368212808981895</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4216,22 +4216,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1264815689694328</v>
+        <v>0.1261448515207883</v>
       </c>
       <c r="C33">
-        <v>1015.549676534954</v>
+        <v>1008.963523626272</v>
       </c>
       <c r="D33">
-        <v>1377.709676534954</v>
+        <v>1383.483523626272</v>
       </c>
       <c r="E33">
-        <v>369.06</v>
+        <v>381.42</v>
       </c>
       <c r="F33">
-        <v>383.16</v>
+        <v>395.52</v>
       </c>
       <c r="G33">
         <v>21</v>
@@ -4252,28 +4252,28 @@
         <v>153.3</v>
       </c>
       <c r="M33">
-        <v>20.805588</v>
+        <v>21.476736</v>
       </c>
       <c r="N33">
-        <v>132.494412</v>
+        <v>131.823264</v>
       </c>
       <c r="O33">
-        <v>38.42337948</v>
+        <v>38.22874656</v>
       </c>
       <c r="P33">
-        <v>94.07103252000002</v>
+        <v>93.59451744000002</v>
       </c>
       <c r="Q33">
-        <v>99.37103252</v>
+        <v>98.89451744</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1659857086513519</v>
+        <v>0.1673645463541005</v>
       </c>
       <c r="T33">
-        <v>0.7350408328272126</v>
+        <v>0.7434736325729956</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>7.368212808981895</v>
+        <v>7.137956158701212</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4298,22 +4298,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1261448515207883</v>
+        <v>0.1258081340721438</v>
       </c>
       <c r="C34">
-        <v>1008.963523626272</v>
+        <v>1002.425969652786</v>
       </c>
       <c r="D34">
-        <v>1383.483523626272</v>
+        <v>1389.305969652786</v>
       </c>
       <c r="E34">
-        <v>381.42</v>
+        <v>393.78</v>
       </c>
       <c r="F34">
-        <v>395.52</v>
+        <v>407.88</v>
       </c>
       <c r="G34">
         <v>21</v>
@@ -4334,28 +4334,28 @@
         <v>153.3</v>
       </c>
       <c r="M34">
-        <v>21.476736</v>
+        <v>22.147884</v>
       </c>
       <c r="N34">
-        <v>131.823264</v>
+        <v>131.152116</v>
       </c>
       <c r="O34">
-        <v>38.22874656</v>
+        <v>38.03411364</v>
       </c>
       <c r="P34">
-        <v>93.59451744000002</v>
+        <v>93.11800236000001</v>
       </c>
       <c r="Q34">
-        <v>98.89451744</v>
+        <v>98.41800235999999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1673645463541005</v>
+        <v>0.1687845433912594</v>
       </c>
       <c r="T34">
-        <v>0.7434736325729956</v>
+        <v>0.7521581576843243</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4372,7 +4372,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>7.137956158701212</v>
+        <v>6.921654456922385</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4380,22 +4380,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1258081340721438</v>
+        <v>0.1254714166234993</v>
       </c>
       <c r="C35">
-        <v>1002.425969652786</v>
+        <v>995.9376307994519</v>
       </c>
       <c r="D35">
-        <v>1389.305969652786</v>
+        <v>1395.177630799452</v>
       </c>
       <c r="E35">
-        <v>393.78</v>
+        <v>406.14</v>
       </c>
       <c r="F35">
-        <v>407.88</v>
+        <v>420.24</v>
       </c>
       <c r="G35">
         <v>21</v>
@@ -4416,28 +4416,28 @@
         <v>153.3</v>
       </c>
       <c r="M35">
-        <v>22.147884</v>
+        <v>22.819032</v>
       </c>
       <c r="N35">
-        <v>131.152116</v>
+        <v>130.480968</v>
       </c>
       <c r="O35">
-        <v>38.03411364</v>
+        <v>37.83948072</v>
       </c>
       <c r="P35">
-        <v>93.11800236000001</v>
+        <v>92.64148728000001</v>
       </c>
       <c r="Q35">
-        <v>98.41800235999999</v>
+        <v>97.94148727999999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1687845433912594</v>
+        <v>0.1702475706416656</v>
       </c>
       <c r="T35">
-        <v>0.7521581576843243</v>
+        <v>0.7611058502232689</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4454,7 +4454,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.921654456922385</v>
+        <v>6.718076384659963</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4462,22 +4462,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1254714166234993</v>
+        <v>0.1251346991748548</v>
       </c>
       <c r="C36">
-        <v>995.9376307994519</v>
+        <v>989.4991337122343</v>
       </c>
       <c r="D36">
-        <v>1395.177630799452</v>
+        <v>1401.099133712234</v>
       </c>
       <c r="E36">
-        <v>406.14</v>
+        <v>418.5</v>
       </c>
       <c r="F36">
-        <v>420.24</v>
+        <v>432.6</v>
       </c>
       <c r="G36">
         <v>21</v>
@@ -4498,28 +4498,28 @@
         <v>153.3</v>
       </c>
       <c r="M36">
-        <v>22.819032</v>
+        <v>23.49018</v>
       </c>
       <c r="N36">
-        <v>130.480968</v>
+        <v>129.80982</v>
       </c>
       <c r="O36">
-        <v>37.83948072</v>
+        <v>37.6448478</v>
       </c>
       <c r="P36">
-        <v>92.64148728000001</v>
+        <v>92.16497219999999</v>
       </c>
       <c r="Q36">
-        <v>97.94148727999999</v>
+        <v>97.46497219999998</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1702475706416656</v>
+        <v>0.1717556141151613</v>
       </c>
       <c r="T36">
-        <v>0.7611058502232689</v>
+        <v>0.7703288563787968</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4536,7 +4536,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>6.718076384659963</v>
+        <v>6.526131345098249</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4544,22 +4544,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1251346991748548</v>
+        <v>0.1247979817262103</v>
       </c>
       <c r="C37">
-        <v>989.4991337122343</v>
+        <v>983.1111157210496</v>
       </c>
       <c r="D37">
-        <v>1401.099133712234</v>
+        <v>1407.07111572105</v>
       </c>
       <c r="E37">
-        <v>418.5</v>
+        <v>430.86</v>
       </c>
       <c r="F37">
-        <v>432.6</v>
+        <v>444.96</v>
       </c>
       <c r="G37">
         <v>21</v>
@@ -4580,28 +4580,28 @@
         <v>153.3</v>
       </c>
       <c r="M37">
-        <v>23.49018</v>
+        <v>24.161328</v>
       </c>
       <c r="N37">
-        <v>129.80982</v>
+        <v>129.138672</v>
       </c>
       <c r="O37">
-        <v>37.6448478</v>
+        <v>37.45021488</v>
       </c>
       <c r="P37">
-        <v>92.16497219999999</v>
+        <v>91.68845712000001</v>
       </c>
       <c r="Q37">
-        <v>97.46497219999998</v>
+        <v>96.98845711999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1717556141151613</v>
+        <v>0.1733107839472036</v>
       </c>
       <c r="T37">
-        <v>0.7703288563787968</v>
+        <v>0.7798400814766846</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4618,7 +4618,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>6.526131345098249</v>
+        <v>6.344849918845521</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4626,22 +4626,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1247979817262103</v>
+        <v>0.1244612642775658</v>
       </c>
       <c r="C38">
-        <v>983.1111157210494</v>
+        <v>976.7742250684296</v>
       </c>
       <c r="D38">
-        <v>1407.071115721049</v>
+        <v>1413.09422506843</v>
       </c>
       <c r="E38">
-        <v>430.86</v>
+        <v>443.22</v>
       </c>
       <c r="F38">
-        <v>444.96</v>
+        <v>457.32</v>
       </c>
       <c r="G38">
         <v>21</v>
@@ -4662,28 +4662,28 @@
         <v>153.3</v>
       </c>
       <c r="M38">
-        <v>24.161328</v>
+        <v>24.832476</v>
       </c>
       <c r="N38">
-        <v>129.138672</v>
+        <v>128.467524</v>
       </c>
       <c r="O38">
-        <v>37.45021488</v>
+        <v>37.25558196000001</v>
       </c>
       <c r="P38">
-        <v>91.68845712000001</v>
+        <v>91.21194204000003</v>
       </c>
       <c r="Q38">
-        <v>96.98845711999999</v>
+        <v>96.51194204000001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1733107839472036</v>
+        <v>0.1749153242501045</v>
       </c>
       <c r="T38">
-        <v>0.7798400814766846</v>
+        <v>0.7896532502284737</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4700,7 +4700,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>6.344849918845521</v>
+        <v>6.173367488606454</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4708,22 +4708,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1244612642775658</v>
+        <v>0.1243943468289213</v>
       </c>
       <c r="C39">
-        <v>976.7742250684296</v>
+        <v>965.6173734378879</v>
       </c>
       <c r="D39">
-        <v>1413.09422506843</v>
+        <v>1414.297373437888</v>
       </c>
       <c r="E39">
-        <v>443.22</v>
+        <v>455.58</v>
       </c>
       <c r="F39">
-        <v>457.32</v>
+        <v>469.68</v>
       </c>
       <c r="G39">
         <v>21</v>
@@ -4744,45 +4744,45 @@
         <v>153.3</v>
       </c>
       <c r="M39">
-        <v>24.832476</v>
+        <v>25.973304</v>
       </c>
       <c r="N39">
-        <v>128.467524</v>
+        <v>127.326696</v>
       </c>
       <c r="O39">
-        <v>37.25558196000001</v>
+        <v>36.92474184</v>
       </c>
       <c r="P39">
-        <v>91.21194204000003</v>
+        <v>90.40195416</v>
       </c>
       <c r="Q39">
-        <v>96.51194204000001</v>
+        <v>95.70195415999999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1749153242501045</v>
+        <v>0.1765716239176151</v>
       </c>
       <c r="T39">
-        <v>0.7896532502284737</v>
+        <v>0.7997829728109656</v>
       </c>
       <c r="U39">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V39">
         <v>0.29</v>
       </c>
       <c r="W39">
-        <v>0.038553</v>
+        <v>0.039263</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y39">
-        <v>6.173367488606454</v>
+        <v>5.902214057941954</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4790,22 +4790,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1243943468289213</v>
+        <v>0.1240647293802769</v>
       </c>
       <c r="C40">
-        <v>965.6173734378879</v>
+        <v>959.2137869532544</v>
       </c>
       <c r="D40">
-        <v>1414.297373437888</v>
+        <v>1420.253786953254</v>
       </c>
       <c r="E40">
-        <v>455.58</v>
+        <v>467.94</v>
       </c>
       <c r="F40">
-        <v>469.68</v>
+        <v>482.04</v>
       </c>
       <c r="G40">
         <v>21</v>
@@ -4826,28 +4826,28 @@
         <v>153.3</v>
       </c>
       <c r="M40">
-        <v>25.973304</v>
+        <v>26.656812</v>
       </c>
       <c r="N40">
-        <v>127.326696</v>
+        <v>126.643188</v>
       </c>
       <c r="O40">
-        <v>36.92474184</v>
+        <v>36.72652452</v>
       </c>
       <c r="P40">
-        <v>90.40195416</v>
+        <v>89.91666348000001</v>
       </c>
       <c r="Q40">
-        <v>95.70195415999999</v>
+        <v>95.21666347999999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1765716239176151</v>
+        <v>0.1782822284922571</v>
       </c>
       <c r="T40">
-        <v>0.7997829728109656</v>
+        <v>0.8102448174453426</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4864,7 +4864,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.902214057941954</v>
+        <v>5.750875235943443</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4872,22 +4872,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1240647293802769</v>
+        <v>0.1237351119316324</v>
       </c>
       <c r="C41">
-        <v>959.2137869532544</v>
+        <v>952.8605843784494</v>
       </c>
       <c r="D41">
-        <v>1420.253786953254</v>
+        <v>1426.260584378449</v>
       </c>
       <c r="E41">
-        <v>467.94</v>
+        <v>480.3</v>
       </c>
       <c r="F41">
-        <v>482.04</v>
+        <v>494.4</v>
       </c>
       <c r="G41">
         <v>21</v>
@@ -4908,28 +4908,28 @@
         <v>153.3</v>
       </c>
       <c r="M41">
-        <v>26.656812</v>
+        <v>27.34032</v>
       </c>
       <c r="N41">
-        <v>126.643188</v>
+        <v>125.95968</v>
       </c>
       <c r="O41">
-        <v>36.72652452</v>
+        <v>36.5283072</v>
       </c>
       <c r="P41">
-        <v>89.91666348000001</v>
+        <v>89.43137280000001</v>
       </c>
       <c r="Q41">
-        <v>95.21666347999999</v>
+        <v>94.73137279999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1782822284922571</v>
+        <v>0.1800498532193873</v>
       </c>
       <c r="T41">
-        <v>0.8102448174453426</v>
+        <v>0.8210553902341988</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4946,7 +4946,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.750875235943443</v>
+        <v>5.607103355044857</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4954,22 +4954,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1237351119316324</v>
+        <v>0.1234054944829878</v>
       </c>
       <c r="C42">
-        <v>952.8605843784494</v>
+        <v>946.5584077072874</v>
       </c>
       <c r="D42">
-        <v>1426.260584378449</v>
+        <v>1432.318407707287</v>
       </c>
       <c r="E42">
-        <v>480.3</v>
+        <v>492.66</v>
       </c>
       <c r="F42">
-        <v>494.4</v>
+        <v>506.76</v>
       </c>
       <c r="G42">
         <v>21</v>
@@ -4990,28 +4990,28 @@
         <v>153.3</v>
       </c>
       <c r="M42">
-        <v>27.34032</v>
+        <v>28.02382800000001</v>
       </c>
       <c r="N42">
-        <v>125.95968</v>
+        <v>125.276172</v>
       </c>
       <c r="O42">
-        <v>36.5283072</v>
+        <v>36.33008988</v>
       </c>
       <c r="P42">
-        <v>89.43137280000001</v>
+        <v>88.94608212</v>
       </c>
       <c r="Q42">
-        <v>94.73137279999999</v>
+        <v>94.24608211999998</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1800498532193873</v>
+        <v>0.181877397428793</v>
       </c>
       <c r="T42">
-        <v>0.8210553902341988</v>
+        <v>0.8322324231175924</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -5028,7 +5028,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.607103355044857</v>
+        <v>5.470344736629128</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5036,22 +5036,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1234054944829878</v>
+        <v>0.1230758770343433</v>
       </c>
       <c r="C43">
-        <v>946.5584077072874</v>
+        <v>940.3079098871882</v>
       </c>
       <c r="D43">
-        <v>1432.318407707287</v>
+        <v>1438.427909887188</v>
       </c>
       <c r="E43">
-        <v>492.66</v>
+        <v>505.02</v>
       </c>
       <c r="F43">
-        <v>506.76</v>
+        <v>519.12</v>
       </c>
       <c r="G43">
         <v>21</v>
@@ -5072,28 +5072,28 @@
         <v>153.3</v>
       </c>
       <c r="M43">
-        <v>28.02382800000001</v>
+        <v>28.707336</v>
       </c>
       <c r="N43">
-        <v>125.276172</v>
+        <v>124.592664</v>
       </c>
       <c r="O43">
-        <v>36.33008988</v>
+        <v>36.13187256</v>
       </c>
       <c r="P43">
-        <v>88.94608212</v>
+        <v>88.46079144000001</v>
       </c>
       <c r="Q43">
-        <v>94.24608211999998</v>
+        <v>93.76079143999999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.181877397428793</v>
+        <v>0.1837679604040403</v>
       </c>
       <c r="T43">
-        <v>0.8322324231175924</v>
+        <v>0.8437948709279997</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -5110,7 +5110,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.470344736629128</v>
+        <v>5.340098433376054</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5118,22 +5118,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1230758770343434</v>
+        <v>0.1227462595856989</v>
       </c>
       <c r="C44">
-        <v>940.3079098871875</v>
+        <v>934.109755053787</v>
       </c>
       <c r="D44">
-        <v>1438.427909887188</v>
+        <v>1444.589755053787</v>
       </c>
       <c r="E44">
-        <v>505.02</v>
+        <v>517.38</v>
       </c>
       <c r="F44">
-        <v>519.12</v>
+        <v>531.48</v>
       </c>
       <c r="G44">
         <v>21</v>
@@ -5154,28 +5154,28 @@
         <v>153.3</v>
       </c>
       <c r="M44">
-        <v>28.707336</v>
+        <v>29.390844</v>
       </c>
       <c r="N44">
-        <v>124.592664</v>
+        <v>123.909156</v>
       </c>
       <c r="O44">
-        <v>36.13187256</v>
+        <v>35.93365524</v>
       </c>
       <c r="P44">
-        <v>88.46079144000001</v>
+        <v>87.97550076000002</v>
       </c>
       <c r="Q44">
-        <v>93.76079143999999</v>
+        <v>93.27550076</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1837679604040403</v>
+        <v>0.1857248589222787</v>
       </c>
       <c r="T44">
-        <v>0.8437948709279997</v>
+        <v>0.8557630186615791</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -5192,7 +5192,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.340098433376054</v>
+        <v>5.215910097716146</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5200,22 +5200,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1227462595856989</v>
+        <v>0.1224166421370544</v>
       </c>
       <c r="C45">
-        <v>934.109755053787</v>
+        <v>927.964618771607</v>
       </c>
       <c r="D45">
-        <v>1444.589755053787</v>
+        <v>1450.804618771607</v>
       </c>
       <c r="E45">
-        <v>517.38</v>
+        <v>529.74</v>
       </c>
       <c r="F45">
-        <v>531.48</v>
+        <v>543.84</v>
       </c>
       <c r="G45">
         <v>21</v>
@@ -5236,28 +5236,28 @@
         <v>153.3</v>
       </c>
       <c r="M45">
-        <v>29.390844</v>
+        <v>30.074352</v>
       </c>
       <c r="N45">
-        <v>123.909156</v>
+        <v>123.225648</v>
       </c>
       <c r="O45">
-        <v>35.93365524</v>
+        <v>35.73543792</v>
       </c>
       <c r="P45">
-        <v>87.97550076000002</v>
+        <v>87.49021008</v>
       </c>
       <c r="Q45">
-        <v>93.27550076</v>
+        <v>92.79021007999998</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1857248589222787</v>
+        <v>0.1877516466733114</v>
       </c>
       <c r="T45">
-        <v>0.8557630186615791</v>
+        <v>0.8681586002427865</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5274,7 +5274,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.215910097716146</v>
+        <v>5.097366686404415</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5282,22 +5282,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1224166421370544</v>
+        <v>0.1220870246884099</v>
       </c>
       <c r="C46">
-        <v>927.964618771607</v>
+        <v>921.873188280962</v>
       </c>
       <c r="D46">
-        <v>1450.804618771607</v>
+        <v>1457.073188280962</v>
       </c>
       <c r="E46">
-        <v>529.74</v>
+        <v>542.1</v>
       </c>
       <c r="F46">
-        <v>543.84</v>
+        <v>556.2</v>
       </c>
       <c r="G46">
         <v>21</v>
@@ -5318,28 +5318,28 @@
         <v>153.3</v>
       </c>
       <c r="M46">
-        <v>30.074352</v>
+        <v>30.75786</v>
       </c>
       <c r="N46">
-        <v>123.225648</v>
+        <v>122.54214</v>
       </c>
       <c r="O46">
-        <v>35.73543792</v>
+        <v>35.5372206</v>
       </c>
       <c r="P46">
-        <v>87.49021008</v>
+        <v>87.00491940000001</v>
       </c>
       <c r="Q46">
-        <v>92.79021007999998</v>
+        <v>92.30491939999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1877516466733114</v>
+        <v>0.1898521357971089</v>
       </c>
       <c r="T46">
-        <v>0.8681586002427865</v>
+        <v>0.8810049302451285</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5356,7 +5356,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.097366686404415</v>
+        <v>4.984091871150984</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5364,22 +5364,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1220870246884099</v>
+        <v>0.1217574072397654</v>
       </c>
       <c r="C47">
-        <v>921.873188280962</v>
+        <v>915.836162751291</v>
       </c>
       <c r="D47">
-        <v>1457.073188280962</v>
+        <v>1463.396162751291</v>
       </c>
       <c r="E47">
-        <v>542.1</v>
+        <v>554.46</v>
       </c>
       <c r="F47">
-        <v>556.2</v>
+        <v>568.5600000000001</v>
       </c>
       <c r="G47">
         <v>21</v>
@@ -5400,28 +5400,28 @@
         <v>153.3</v>
       </c>
       <c r="M47">
-        <v>30.75786</v>
+        <v>31.441368</v>
       </c>
       <c r="N47">
-        <v>122.54214</v>
+        <v>121.858632</v>
       </c>
       <c r="O47">
-        <v>35.5372206</v>
+        <v>35.33900328</v>
       </c>
       <c r="P47">
-        <v>87.00491940000001</v>
+        <v>86.51962872</v>
       </c>
       <c r="Q47">
-        <v>92.30491939999999</v>
+        <v>91.81962871999998</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1898521357971089</v>
+        <v>0.1920304208143803</v>
       </c>
       <c r="T47">
-        <v>0.8810049302451285</v>
+        <v>0.8943270502475574</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5438,7 +5438,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.984091871150984</v>
+        <v>4.875742047865092</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5446,22 +5446,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1217574072397654</v>
+        <v>0.1214277897911209</v>
       </c>
       <c r="C48">
-        <v>915.836162751291</v>
+        <v>909.8542535411248</v>
       </c>
       <c r="D48">
-        <v>1463.396162751291</v>
+        <v>1469.774253541125</v>
       </c>
       <c r="E48">
-        <v>554.46</v>
+        <v>566.8200000000001</v>
       </c>
       <c r="F48">
-        <v>568.5600000000001</v>
+        <v>580.9200000000001</v>
       </c>
       <c r="G48">
         <v>21</v>
@@ -5482,28 +5482,28 @@
         <v>153.3</v>
       </c>
       <c r="M48">
-        <v>31.441368</v>
+        <v>32.12487600000001</v>
       </c>
       <c r="N48">
-        <v>121.858632</v>
+        <v>121.175124</v>
       </c>
       <c r="O48">
-        <v>35.33900328</v>
+        <v>35.14078596</v>
       </c>
       <c r="P48">
-        <v>86.51962872</v>
+        <v>86.03433804000001</v>
       </c>
       <c r="Q48">
-        <v>91.81962871999998</v>
+        <v>91.33433803999999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1920304208143803</v>
+        <v>0.1942909052662658</v>
       </c>
       <c r="T48">
-        <v>0.8943270502475574</v>
+        <v>0.9081518917595118</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5520,7 +5520,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.875742047865092</v>
+        <v>4.772002855357325</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5528,22 +5528,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1214277897911209</v>
+        <v>0.1210981723424764</v>
       </c>
       <c r="C49">
-        <v>909.8542535411248</v>
+        <v>903.928184464868</v>
       </c>
       <c r="D49">
-        <v>1469.774253541125</v>
+        <v>1476.208184464868</v>
       </c>
       <c r="E49">
-        <v>566.8200000000001</v>
+        <v>579.1800000000001</v>
       </c>
       <c r="F49">
-        <v>580.9200000000001</v>
+        <v>593.2800000000001</v>
       </c>
       <c r="G49">
         <v>21</v>
@@ -5564,28 +5564,28 @@
         <v>153.3</v>
       </c>
       <c r="M49">
-        <v>32.12487600000001</v>
+        <v>32.808384</v>
       </c>
       <c r="N49">
-        <v>121.175124</v>
+        <v>120.491616</v>
       </c>
       <c r="O49">
-        <v>35.14078596</v>
+        <v>34.94256864</v>
       </c>
       <c r="P49">
-        <v>86.03433804000001</v>
+        <v>85.54904736</v>
       </c>
       <c r="Q49">
-        <v>91.33433803999999</v>
+        <v>90.84904735999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1942909052662658</v>
+        <v>0.1966383314278392</v>
       </c>
       <c r="T49">
-        <v>0.9081518917595118</v>
+        <v>0.922508457945003</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5602,7 +5602,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.772002855357325</v>
+        <v>4.672586129204047</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5610,22 +5610,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1210981723424764</v>
+        <v>0.1207685548938319</v>
       </c>
       <c r="C50">
-        <v>903.9281844648681</v>
+        <v>898.0586920666291</v>
       </c>
       <c r="D50">
-        <v>1476.208184464868</v>
+        <v>1482.698692066629</v>
       </c>
       <c r="E50">
-        <v>579.1799999999999</v>
+        <v>591.54</v>
       </c>
       <c r="F50">
-        <v>593.28</v>
+        <v>605.64</v>
       </c>
       <c r="G50">
         <v>21</v>
@@ -5646,28 +5646,28 @@
         <v>153.3</v>
       </c>
       <c r="M50">
-        <v>32.808384</v>
+        <v>33.491892</v>
       </c>
       <c r="N50">
-        <v>120.491616</v>
+        <v>119.808108</v>
       </c>
       <c r="O50">
-        <v>34.94256864</v>
+        <v>34.74435132</v>
       </c>
       <c r="P50">
-        <v>85.54904736000002</v>
+        <v>85.06375668000001</v>
       </c>
       <c r="Q50">
-        <v>90.84904736</v>
+        <v>90.36375667999999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1966383314278392</v>
+        <v>0.1990778135173174</v>
       </c>
       <c r="T50">
-        <v>0.922508457945003</v>
+        <v>0.9374280267260037</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5684,7 +5684,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.672586129204048</v>
+        <v>4.577227228608047</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5692,22 +5692,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1207685548938319</v>
+        <v>0.1213264374451874</v>
       </c>
       <c r="C51">
-        <v>898.0586920666291</v>
+        <v>874.7466101572727</v>
       </c>
       <c r="D51">
-        <v>1482.698692066629</v>
+        <v>1471.746610157273</v>
       </c>
       <c r="E51">
-        <v>591.54</v>
+        <v>603.9</v>
       </c>
       <c r="F51">
-        <v>605.64</v>
+        <v>618</v>
       </c>
       <c r="G51">
         <v>21</v>
@@ -5728,45 +5728,45 @@
         <v>153.3</v>
       </c>
       <c r="M51">
-        <v>33.491892</v>
+        <v>35.72040000000001</v>
       </c>
       <c r="N51">
-        <v>119.808108</v>
+        <v>117.5796</v>
       </c>
       <c r="O51">
-        <v>34.74435132</v>
+        <v>34.098084</v>
       </c>
       <c r="P51">
-        <v>85.06375668000001</v>
+        <v>83.481516</v>
       </c>
       <c r="Q51">
-        <v>90.36375667999999</v>
+        <v>88.78151599999998</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1990778135173174</v>
+        <v>0.2016148748903748</v>
       </c>
       <c r="T51">
-        <v>0.9374280267260037</v>
+        <v>0.9529443782582443</v>
       </c>
       <c r="U51">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V51">
         <v>0.29</v>
       </c>
       <c r="W51">
-        <v>0.039263</v>
+        <v>0.041038</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y51">
-        <v>4.577227228608047</v>
+        <v>4.291665266906305</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5774,22 +5774,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1213264374451874</v>
+        <v>0.1210145699965429</v>
       </c>
       <c r="C52">
-        <v>874.7466101572727</v>
+        <v>868.4890163849756</v>
       </c>
       <c r="D52">
-        <v>1471.746610157273</v>
+        <v>1477.849016384976</v>
       </c>
       <c r="E52">
-        <v>603.9</v>
+        <v>616.26</v>
       </c>
       <c r="F52">
-        <v>618</v>
+        <v>630.36</v>
       </c>
       <c r="G52">
         <v>21</v>
@@ -5810,28 +5810,28 @@
         <v>153.3</v>
       </c>
       <c r="M52">
-        <v>35.72040000000001</v>
+        <v>36.434808</v>
       </c>
       <c r="N52">
-        <v>117.5796</v>
+        <v>116.865192</v>
       </c>
       <c r="O52">
-        <v>34.098084</v>
+        <v>33.89090568</v>
       </c>
       <c r="P52">
-        <v>83.481516</v>
+        <v>82.97428632</v>
       </c>
       <c r="Q52">
-        <v>88.78151599999998</v>
+        <v>88.27428631999999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2016148748903748</v>
+        <v>0.2042554897888631</v>
       </c>
       <c r="T52">
-        <v>0.9529443782582443</v>
+        <v>0.9690940502611887</v>
       </c>
       <c r="U52">
         <v>0.0578</v>
@@ -5848,7 +5848,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.291665266906305</v>
+        <v>4.207514967555202</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5856,22 +5856,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1210145699965429</v>
+        <v>0.1207027025478984</v>
       </c>
       <c r="C53">
-        <v>868.4890163849756</v>
+        <v>862.28223898635</v>
       </c>
       <c r="D53">
-        <v>1477.849016384976</v>
+        <v>1484.00223898635</v>
       </c>
       <c r="E53">
-        <v>616.26</v>
+        <v>628.62</v>
       </c>
       <c r="F53">
-        <v>630.36</v>
+        <v>642.72</v>
       </c>
       <c r="G53">
         <v>21</v>
@@ -5892,28 +5892,28 @@
         <v>153.3</v>
       </c>
       <c r="M53">
-        <v>36.434808</v>
+        <v>37.149216</v>
       </c>
       <c r="N53">
-        <v>116.865192</v>
+        <v>116.150784</v>
       </c>
       <c r="O53">
-        <v>33.89090568</v>
+        <v>33.68372736</v>
       </c>
       <c r="P53">
-        <v>82.97428632</v>
+        <v>82.46705664000001</v>
       </c>
       <c r="Q53">
-        <v>88.27428631999999</v>
+        <v>87.76705663999999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2042554897888631</v>
+        <v>0.2070061303081217</v>
       </c>
       <c r="T53">
-        <v>0.9690940502611887</v>
+        <v>0.9859166252642557</v>
       </c>
       <c r="U53">
         <v>0.0578</v>
@@ -5930,7 +5930,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.207514967555202</v>
+        <v>4.12660121817914</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5938,22 +5938,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1207027025478984</v>
+        <v>0.1203908350992539</v>
       </c>
       <c r="C54">
-        <v>862.28223898635</v>
+        <v>856.1269153576433</v>
       </c>
       <c r="D54">
-        <v>1484.00223898635</v>
+        <v>1490.206915357643</v>
       </c>
       <c r="E54">
-        <v>628.62</v>
+        <v>640.98</v>
       </c>
       <c r="F54">
-        <v>642.72</v>
+        <v>655.08</v>
       </c>
       <c r="G54">
         <v>21</v>
@@ -5974,28 +5974,28 @@
         <v>153.3</v>
       </c>
       <c r="M54">
-        <v>37.149216</v>
+        <v>37.86362400000001</v>
       </c>
       <c r="N54">
-        <v>116.150784</v>
+        <v>115.436376</v>
       </c>
       <c r="O54">
-        <v>33.68372736</v>
+        <v>33.47654903999999</v>
       </c>
       <c r="P54">
-        <v>82.46705664000001</v>
+        <v>81.95982696</v>
       </c>
       <c r="Q54">
-        <v>87.76705663999999</v>
+        <v>87.25982695999998</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2070061303081217</v>
+        <v>0.2098738193601147</v>
       </c>
       <c r="T54">
-        <v>0.9859166252642557</v>
+        <v>1.003455054522773</v>
       </c>
       <c r="U54">
         <v>0.0578</v>
@@ -6012,7 +6012,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.12660121817914</v>
+        <v>4.048740817836137</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -6020,22 +6020,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1203908350992539</v>
+        <v>0.1214208676506094</v>
       </c>
       <c r="C55">
-        <v>856.1269153576433</v>
+        <v>823.4687929112654</v>
       </c>
       <c r="D55">
-        <v>1490.206915357643</v>
+        <v>1469.908792911265</v>
       </c>
       <c r="E55">
-        <v>640.98</v>
+        <v>653.34</v>
       </c>
       <c r="F55">
-        <v>655.08</v>
+        <v>667.4400000000001</v>
       </c>
       <c r="G55">
         <v>21</v>
@@ -6056,45 +6056,45 @@
         <v>153.3</v>
       </c>
       <c r="M55">
-        <v>37.86362400000001</v>
+        <v>40.914072</v>
       </c>
       <c r="N55">
-        <v>115.436376</v>
+        <v>112.385928</v>
       </c>
       <c r="O55">
-        <v>33.47654903999999</v>
+        <v>32.59191912</v>
       </c>
       <c r="P55">
-        <v>81.95982696</v>
+        <v>79.79400888000001</v>
       </c>
       <c r="Q55">
-        <v>87.25982695999998</v>
+        <v>85.09400887999999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2098738193601147</v>
+        <v>0.2128661905448031</v>
       </c>
       <c r="T55">
-        <v>1.003455054522773</v>
+        <v>1.021756024183833</v>
       </c>
       <c r="U55">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V55">
         <v>0.29</v>
       </c>
       <c r="W55">
-        <v>0.041038</v>
+        <v>0.043523</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y55">
-        <v>4.048740817836137</v>
+        <v>3.746877113575984</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6102,22 +6102,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1214208676506094</v>
+        <v>0.1211338502019649</v>
       </c>
       <c r="C56">
-        <v>823.4687929112654</v>
+        <v>816.7090572061401</v>
       </c>
       <c r="D56">
-        <v>1469.908792911265</v>
+        <v>1475.50905720614</v>
       </c>
       <c r="E56">
-        <v>653.34</v>
+        <v>665.7</v>
       </c>
       <c r="F56">
-        <v>667.4400000000001</v>
+        <v>679.8000000000001</v>
       </c>
       <c r="G56">
         <v>21</v>
@@ -6138,28 +6138,28 @@
         <v>153.3</v>
       </c>
       <c r="M56">
-        <v>40.914072</v>
+        <v>41.67174000000001</v>
       </c>
       <c r="N56">
-        <v>112.385928</v>
+        <v>111.62826</v>
       </c>
       <c r="O56">
-        <v>32.59191912</v>
+        <v>32.3721954</v>
       </c>
       <c r="P56">
-        <v>79.79400888000001</v>
+        <v>79.2560646</v>
       </c>
       <c r="Q56">
-        <v>85.09400887999999</v>
+        <v>84.55606459999998</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2128661905448031</v>
+        <v>0.2159915560043665</v>
       </c>
       <c r="T56">
-        <v>1.021756024183833</v>
+        <v>1.040870370274275</v>
       </c>
       <c r="U56">
         <v>0.0613</v>
@@ -6176,7 +6176,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.746877113575984</v>
+        <v>3.67875207514733</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6184,22 +6184,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1211338502019649</v>
+        <v>0.1208468327533204</v>
       </c>
       <c r="C57">
-        <v>816.7090572061401</v>
+        <v>809.9921580474929</v>
       </c>
       <c r="D57">
-        <v>1475.50905720614</v>
+        <v>1481.152158047493</v>
       </c>
       <c r="E57">
-        <v>665.7</v>
+        <v>678.0600000000001</v>
       </c>
       <c r="F57">
-        <v>679.8000000000001</v>
+        <v>692.1600000000001</v>
       </c>
       <c r="G57">
         <v>21</v>
@@ -6220,28 +6220,28 @@
         <v>153.3</v>
       </c>
       <c r="M57">
-        <v>41.67174000000001</v>
+        <v>42.429408</v>
       </c>
       <c r="N57">
-        <v>111.62826</v>
+        <v>110.870592</v>
       </c>
       <c r="O57">
-        <v>32.3721954</v>
+        <v>32.15247168</v>
       </c>
       <c r="P57">
-        <v>79.2560646</v>
+        <v>78.71812032000001</v>
       </c>
       <c r="Q57">
-        <v>84.55606459999998</v>
+        <v>84.01812031999999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2159915560043665</v>
+        <v>0.2192589835302737</v>
       </c>
       <c r="T57">
-        <v>1.040870370274275</v>
+        <v>1.060853550277918</v>
       </c>
       <c r="U57">
         <v>0.0613</v>
@@ -6258,7 +6258,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.67875207514733</v>
+        <v>3.613060073805414</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6266,22 +6266,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1208468327533204</v>
+        <v>0.1205598153046759</v>
       </c>
       <c r="C58">
-        <v>809.9921580474929</v>
+        <v>803.3185888087859</v>
       </c>
       <c r="D58">
-        <v>1481.152158047493</v>
+        <v>1486.838588808786</v>
       </c>
       <c r="E58">
-        <v>678.0600000000001</v>
+        <v>690.4200000000001</v>
       </c>
       <c r="F58">
-        <v>692.1600000000001</v>
+        <v>704.5200000000001</v>
       </c>
       <c r="G58">
         <v>21</v>
@@ -6302,28 +6302,28 @@
         <v>153.3</v>
       </c>
       <c r="M58">
-        <v>42.429408</v>
+        <v>43.187076</v>
       </c>
       <c r="N58">
-        <v>110.870592</v>
+        <v>110.112924</v>
       </c>
       <c r="O58">
-        <v>32.15247168</v>
+        <v>31.93274796</v>
       </c>
       <c r="P58">
-        <v>78.71812032000001</v>
+        <v>78.18017604000001</v>
       </c>
       <c r="Q58">
-        <v>84.01812031999999</v>
+        <v>83.48017603999999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2192589835302737</v>
+        <v>0.2226783844294789</v>
       </c>
       <c r="T58">
-        <v>1.060853550277918</v>
+        <v>1.081766180514289</v>
       </c>
       <c r="U58">
         <v>0.0613</v>
@@ -6340,7 +6340,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.613060073805414</v>
+        <v>3.549673054966722</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6348,22 +6348,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1205598153046759</v>
+        <v>0.1214258378560314</v>
       </c>
       <c r="C59">
-        <v>803.3185888087859</v>
+        <v>773.9321890406895</v>
       </c>
       <c r="D59">
-        <v>1486.838588808786</v>
+        <v>1469.81218904069</v>
       </c>
       <c r="E59">
-        <v>690.4200000000001</v>
+        <v>702.7800000000001</v>
       </c>
       <c r="F59">
-        <v>704.5200000000001</v>
+        <v>716.8800000000001</v>
       </c>
       <c r="G59">
         <v>21</v>
@@ -6384,45 +6384,45 @@
         <v>153.3</v>
       </c>
       <c r="M59">
-        <v>43.187076</v>
+        <v>45.95200800000001</v>
       </c>
       <c r="N59">
-        <v>110.112924</v>
+        <v>107.347992</v>
       </c>
       <c r="O59">
-        <v>31.93274796</v>
+        <v>31.13091768</v>
       </c>
       <c r="P59">
-        <v>78.18017604000001</v>
+        <v>76.21707432000001</v>
       </c>
       <c r="Q59">
-        <v>83.48017603999999</v>
+        <v>81.51707431999999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2226783844294789</v>
+        <v>0.226260613942932</v>
       </c>
       <c r="T59">
-        <v>1.081766180514289</v>
+        <v>1.103674650285725</v>
       </c>
       <c r="U59">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V59">
         <v>0.29</v>
       </c>
       <c r="W59">
-        <v>0.043523</v>
+        <v>0.045511</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y59">
-        <v>3.549673054966722</v>
+        <v>3.336089252073597</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6430,22 +6430,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1214258378560314</v>
+        <v>0.1211587004073869</v>
       </c>
       <c r="C60">
-        <v>773.9321890406901</v>
+        <v>766.7824948984648</v>
       </c>
       <c r="D60">
-        <v>1469.81218904069</v>
+        <v>1475.022494898465</v>
       </c>
       <c r="E60">
-        <v>702.78</v>
+        <v>715.14</v>
       </c>
       <c r="F60">
-        <v>716.88</v>
+        <v>729.24</v>
       </c>
       <c r="G60">
         <v>21</v>
@@ -6466,28 +6466,28 @@
         <v>153.3</v>
       </c>
       <c r="M60">
-        <v>45.952008</v>
+        <v>46.744284</v>
       </c>
       <c r="N60">
-        <v>107.347992</v>
+        <v>106.555716</v>
       </c>
       <c r="O60">
-        <v>31.13091768</v>
+        <v>30.90115764</v>
       </c>
       <c r="P60">
-        <v>76.21707432000001</v>
+        <v>75.65455836000001</v>
       </c>
       <c r="Q60">
-        <v>81.51707431999999</v>
+        <v>80.95455835999999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.226260613942932</v>
+        <v>0.2300175863594803</v>
       </c>
       <c r="T60">
-        <v>1.103674650285725</v>
+        <v>1.12665182589967</v>
       </c>
       <c r="U60">
         <v>0.0641</v>
@@ -6504,7 +6504,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.336089252073598</v>
+        <v>3.279545366445233</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6512,22 +6512,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1211587004073869</v>
+        <v>0.1208915629587424</v>
       </c>
       <c r="C61">
-        <v>766.7824948984648</v>
+        <v>759.6698719732627</v>
       </c>
       <c r="D61">
-        <v>1475.022494898465</v>
+        <v>1480.269871973263</v>
       </c>
       <c r="E61">
-        <v>715.14</v>
+        <v>727.5</v>
       </c>
       <c r="F61">
-        <v>729.24</v>
+        <v>741.6</v>
       </c>
       <c r="G61">
         <v>21</v>
@@ -6548,28 +6548,28 @@
         <v>153.3</v>
       </c>
       <c r="M61">
-        <v>46.744284</v>
+        <v>47.53656</v>
       </c>
       <c r="N61">
-        <v>106.555716</v>
+        <v>105.76344</v>
       </c>
       <c r="O61">
-        <v>30.90115764</v>
+        <v>30.6713976</v>
       </c>
       <c r="P61">
-        <v>75.65455836000001</v>
+        <v>75.0920424</v>
       </c>
       <c r="Q61">
-        <v>80.95455835999999</v>
+        <v>80.39204239999998</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2300175863594803</v>
+        <v>0.2339624073968561</v>
       </c>
       <c r="T61">
-        <v>1.12665182589967</v>
+        <v>1.150777860294312</v>
       </c>
       <c r="U61">
         <v>0.0641</v>
@@ -6586,7 +6586,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.279545366445233</v>
+        <v>3.224886277004478</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6594,22 +6594,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1208915629587424</v>
+        <v>0.1206244255100979</v>
       </c>
       <c r="C62">
-        <v>759.6698719732627</v>
+        <v>752.5947173189963</v>
       </c>
       <c r="D62">
-        <v>1480.269871973263</v>
+        <v>1485.554717318996</v>
       </c>
       <c r="E62">
-        <v>727.5</v>
+        <v>739.86</v>
       </c>
       <c r="F62">
-        <v>741.6</v>
+        <v>753.96</v>
       </c>
       <c r="G62">
         <v>21</v>
@@ -6630,28 +6630,28 @@
         <v>153.3</v>
       </c>
       <c r="M62">
-        <v>47.53656</v>
+        <v>48.328836</v>
       </c>
       <c r="N62">
-        <v>105.76344</v>
+        <v>104.971164</v>
       </c>
       <c r="O62">
-        <v>30.6713976</v>
+        <v>30.44163756</v>
       </c>
       <c r="P62">
-        <v>75.0920424</v>
+        <v>74.52952644000001</v>
       </c>
       <c r="Q62">
-        <v>80.39204239999998</v>
+        <v>79.82952644</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2339624073968561</v>
+        <v>0.2381095269489691</v>
       </c>
       <c r="T62">
-        <v>1.150777860294312</v>
+        <v>1.176141127222013</v>
       </c>
       <c r="U62">
         <v>0.0641</v>
@@ -6668,7 +6668,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.224886277004478</v>
+        <v>3.172019288856864</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6676,22 +6676,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1206244255100979</v>
+        <v>0.1203572880614534</v>
       </c>
       <c r="C63">
-        <v>752.5947173189963</v>
+        <v>745.5574336801288</v>
       </c>
       <c r="D63">
-        <v>1485.554717318996</v>
+        <v>1490.877433680129</v>
       </c>
       <c r="E63">
-        <v>739.86</v>
+        <v>752.22</v>
       </c>
       <c r="F63">
-        <v>753.96</v>
+        <v>766.3200000000001</v>
       </c>
       <c r="G63">
         <v>21</v>
@@ -6712,28 +6712,28 @@
         <v>153.3</v>
       </c>
       <c r="M63">
-        <v>48.328836</v>
+        <v>49.121112</v>
       </c>
       <c r="N63">
-        <v>104.971164</v>
+        <v>104.178888</v>
       </c>
       <c r="O63">
-        <v>30.44163756</v>
+        <v>30.21187752</v>
       </c>
       <c r="P63">
-        <v>74.52952644000001</v>
+        <v>73.96701048</v>
       </c>
       <c r="Q63">
-        <v>79.82952644</v>
+        <v>79.26701047999998</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2381095269489691</v>
+        <v>0.2424749159511933</v>
       </c>
       <c r="T63">
-        <v>1.176141127222013</v>
+        <v>1.202839302935383</v>
       </c>
       <c r="U63">
         <v>0.0641</v>
@@ -6750,7 +6750,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.172019288856864</v>
+        <v>3.120857687423689</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6758,22 +6758,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1203572880614534</v>
+        <v>0.120090150612809</v>
       </c>
       <c r="C64">
-        <v>745.5574336801288</v>
+        <v>738.5584295939842</v>
       </c>
       <c r="D64">
-        <v>1490.877433680129</v>
+        <v>1496.238429593984</v>
       </c>
       <c r="E64">
-        <v>752.22</v>
+        <v>764.5799999999999</v>
       </c>
       <c r="F64">
-        <v>766.3200000000001</v>
+        <v>778.6799999999999</v>
       </c>
       <c r="G64">
         <v>21</v>
@@ -6794,28 +6794,28 @@
         <v>153.3</v>
       </c>
       <c r="M64">
-        <v>49.121112</v>
+        <v>49.913388</v>
       </c>
       <c r="N64">
-        <v>104.178888</v>
+        <v>103.386612</v>
       </c>
       <c r="O64">
-        <v>30.21187752</v>
+        <v>29.98211748</v>
       </c>
       <c r="P64">
-        <v>73.96701048</v>
+        <v>73.40449452000001</v>
       </c>
       <c r="Q64">
-        <v>79.26701047999998</v>
+        <v>78.70449452</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2424749159511933</v>
+        <v>0.2470762719265107</v>
       </c>
       <c r="T64">
-        <v>1.202839302935383</v>
+        <v>1.230980623281908</v>
       </c>
       <c r="U64">
         <v>0.0641</v>
@@ -6832,7 +6832,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.120857687423689</v>
+        <v>3.071320263813789</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6840,22 +6840,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.120090150612809</v>
+        <v>0.1198230131641645</v>
       </c>
       <c r="C65">
-        <v>738.5584295939842</v>
+        <v>731.5981194952744</v>
       </c>
       <c r="D65">
-        <v>1496.238429593984</v>
+        <v>1501.638119495274</v>
       </c>
       <c r="E65">
-        <v>764.5799999999999</v>
+        <v>776.9399999999999</v>
       </c>
       <c r="F65">
-        <v>778.6799999999999</v>
+        <v>791.04</v>
       </c>
       <c r="G65">
         <v>21</v>
@@ -6876,28 +6876,28 @@
         <v>153.3</v>
       </c>
       <c r="M65">
-        <v>49.913388</v>
+        <v>50.705664</v>
       </c>
       <c r="N65">
-        <v>103.386612</v>
+        <v>102.594336</v>
       </c>
       <c r="O65">
-        <v>29.98211748</v>
+        <v>29.75235744</v>
       </c>
       <c r="P65">
-        <v>73.40449452000001</v>
+        <v>72.84197856000002</v>
       </c>
       <c r="Q65">
-        <v>78.70449452</v>
+        <v>78.14197856</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2470762719265107</v>
+        <v>0.2519332587893457</v>
       </c>
       <c r="T65">
-        <v>1.230980623281908</v>
+        <v>1.26068535031435</v>
       </c>
       <c r="U65">
         <v>0.0641</v>
@@ -6914,7 +6914,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.071320263813789</v>
+        <v>3.023330884691699</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6922,22 +6922,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1198230131641645</v>
+        <v>0.12315557571552</v>
       </c>
       <c r="C66">
-        <v>731.5981194952744</v>
+        <v>654.5459119015835</v>
       </c>
       <c r="D66">
-        <v>1501.638119495274</v>
+        <v>1436.945911901583</v>
       </c>
       <c r="E66">
-        <v>776.9399999999999</v>
+        <v>789.3</v>
       </c>
       <c r="F66">
-        <v>791.04</v>
+        <v>803.4</v>
       </c>
       <c r="G66">
         <v>21</v>
@@ -6958,45 +6958,45 @@
         <v>153.3</v>
       </c>
       <c r="M66">
-        <v>50.705664</v>
+        <v>57.76446</v>
       </c>
       <c r="N66">
-        <v>102.594336</v>
+        <v>95.53554000000001</v>
       </c>
       <c r="O66">
-        <v>29.75235744</v>
+        <v>27.7053066</v>
       </c>
       <c r="P66">
-        <v>72.84197856000002</v>
+        <v>67.83023340000001</v>
       </c>
       <c r="Q66">
-        <v>78.14197856</v>
+        <v>73.13023339999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2519332587893457</v>
+        <v>0.2570677877586285</v>
       </c>
       <c r="T66">
-        <v>1.26068535031435</v>
+        <v>1.292087490320076</v>
       </c>
       <c r="U66">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V66">
         <v>0.29</v>
       </c>
       <c r="W66">
-        <v>0.045511</v>
+        <v>0.051049</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y66">
-        <v>3.023330884691699</v>
+        <v>2.653880950328282</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -7004,22 +7004,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.12315557571552</v>
+        <v>0.1229438182668755</v>
       </c>
       <c r="C67">
-        <v>654.5459119015835</v>
+        <v>646.1302849826743</v>
       </c>
       <c r="D67">
-        <v>1436.945911901583</v>
+        <v>1440.890284982674</v>
       </c>
       <c r="E67">
-        <v>789.3</v>
+        <v>801.66</v>
       </c>
       <c r="F67">
-        <v>803.4</v>
+        <v>815.76</v>
       </c>
       <c r="G67">
         <v>21</v>
@@ -7040,28 +7040,28 @@
         <v>153.3</v>
       </c>
       <c r="M67">
-        <v>57.76446</v>
+        <v>58.653144</v>
       </c>
       <c r="N67">
-        <v>95.53554000000001</v>
+        <v>94.64685600000001</v>
       </c>
       <c r="O67">
-        <v>27.7053066</v>
+        <v>27.44758824</v>
       </c>
       <c r="P67">
-        <v>67.83023340000001</v>
+        <v>67.19926776000001</v>
       </c>
       <c r="Q67">
-        <v>73.13023339999999</v>
+        <v>72.49926776</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2570677877586285</v>
+        <v>0.2625043478437514</v>
       </c>
       <c r="T67">
-        <v>1.292087490320076</v>
+        <v>1.32533681503202</v>
       </c>
       <c r="U67">
         <v>0.07190000000000001</v>
@@ -7078,7 +7078,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.653880950328282</v>
+        <v>2.613670632899065</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7086,22 +7086,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1229438182668755</v>
+        <v>0.122732060818231</v>
       </c>
       <c r="C68">
-        <v>646.1302849826743</v>
+        <v>637.7363720376605</v>
       </c>
       <c r="D68">
-        <v>1440.890284982674</v>
+        <v>1444.856372037661</v>
       </c>
       <c r="E68">
-        <v>801.66</v>
+        <v>814.02</v>
       </c>
       <c r="F68">
-        <v>815.76</v>
+        <v>828.12</v>
       </c>
       <c r="G68">
         <v>21</v>
@@ -7122,28 +7122,28 @@
         <v>153.3</v>
       </c>
       <c r="M68">
-        <v>58.653144</v>
+        <v>59.541828</v>
       </c>
       <c r="N68">
-        <v>94.64685600000001</v>
+        <v>93.758172</v>
       </c>
       <c r="O68">
-        <v>27.44758824</v>
+        <v>27.18986988</v>
       </c>
       <c r="P68">
-        <v>67.19926776000001</v>
+        <v>66.56830212</v>
       </c>
       <c r="Q68">
-        <v>72.49926776</v>
+        <v>71.86830211999998</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2625043478437514</v>
+        <v>0.2682703964188817</v>
       </c>
       <c r="T68">
-        <v>1.32533681503202</v>
+        <v>1.360601250332567</v>
       </c>
       <c r="U68">
         <v>0.07190000000000001</v>
@@ -7160,7 +7160,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.613670632899065</v>
+        <v>2.57466062345281</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7168,22 +7168,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.122732060818231</v>
+        <v>0.1225203033695865</v>
       </c>
       <c r="C69">
-        <v>637.7363720376605</v>
+        <v>629.364352866236</v>
       </c>
       <c r="D69">
-        <v>1444.856372037661</v>
+        <v>1448.844352866236</v>
       </c>
       <c r="E69">
-        <v>814.02</v>
+        <v>826.38</v>
       </c>
       <c r="F69">
-        <v>828.12</v>
+        <v>840.48</v>
       </c>
       <c r="G69">
         <v>21</v>
@@ -7204,28 +7204,28 @@
         <v>153.3</v>
       </c>
       <c r="M69">
-        <v>59.541828</v>
+        <v>60.43051200000001</v>
       </c>
       <c r="N69">
-        <v>93.758172</v>
+        <v>92.869488</v>
       </c>
       <c r="O69">
-        <v>27.18986988</v>
+        <v>26.93215152</v>
       </c>
       <c r="P69">
-        <v>66.56830212</v>
+        <v>65.93733648</v>
       </c>
       <c r="Q69">
-        <v>71.86830211999998</v>
+        <v>71.23733647999998</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2682703964188817</v>
+        <v>0.2743968230299578</v>
       </c>
       <c r="T69">
-        <v>1.360601250332567</v>
+        <v>1.398069712839398</v>
       </c>
       <c r="U69">
         <v>0.07190000000000001</v>
@@ -7242,7 +7242,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.57466062345281</v>
+        <v>2.536797967225563</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7250,22 +7250,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1225203033695865</v>
+        <v>0.122308545920942</v>
       </c>
       <c r="C70">
-        <v>629.364352866236</v>
+        <v>621.0144092586676</v>
       </c>
       <c r="D70">
-        <v>1448.844352866236</v>
+        <v>1452.854409258668</v>
       </c>
       <c r="E70">
-        <v>826.38</v>
+        <v>838.74</v>
       </c>
       <c r="F70">
-        <v>840.48</v>
+        <v>852.84</v>
       </c>
       <c r="G70">
         <v>21</v>
@@ -7286,28 +7286,28 @@
         <v>153.3</v>
       </c>
       <c r="M70">
-        <v>60.43051200000001</v>
+        <v>61.31919600000001</v>
       </c>
       <c r="N70">
-        <v>92.869488</v>
+        <v>91.98080400000001</v>
       </c>
       <c r="O70">
-        <v>26.93215152</v>
+        <v>26.67443316</v>
       </c>
       <c r="P70">
-        <v>65.93733648</v>
+        <v>65.30637084</v>
       </c>
       <c r="Q70">
-        <v>71.23733647999998</v>
+        <v>70.60637083999998</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2743968230299578</v>
+        <v>0.2809185029707806</v>
       </c>
       <c r="T70">
-        <v>1.398069712839398</v>
+        <v>1.43795549550796</v>
       </c>
       <c r="U70">
         <v>0.07190000000000001</v>
@@ -7324,7 +7324,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.536797967225563</v>
+        <v>2.500032779294758</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7332,22 +7332,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.122308545920942</v>
+        <v>0.1240350884722975</v>
       </c>
       <c r="C71">
-        <v>621.0144092586676</v>
+        <v>576.591878142623</v>
       </c>
       <c r="D71">
-        <v>1452.854409258668</v>
+        <v>1420.791878142623</v>
       </c>
       <c r="E71">
-        <v>838.74</v>
+        <v>851.1</v>
       </c>
       <c r="F71">
-        <v>852.84</v>
+        <v>865.2</v>
       </c>
       <c r="G71">
         <v>21</v>
@@ -7368,45 +7368,45 @@
         <v>153.3</v>
       </c>
       <c r="M71">
-        <v>61.31919600000001</v>
+        <v>65.58216</v>
       </c>
       <c r="N71">
-        <v>91.98080400000001</v>
+        <v>87.71784000000001</v>
       </c>
       <c r="O71">
-        <v>26.67443316</v>
+        <v>25.4381736</v>
       </c>
       <c r="P71">
-        <v>65.30637084</v>
+        <v>62.27966640000001</v>
       </c>
       <c r="Q71">
-        <v>70.60637083999998</v>
+        <v>67.57966639999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2809185029707806</v>
+        <v>0.287874961574325</v>
       </c>
       <c r="T71">
-        <v>1.43795549550796</v>
+        <v>1.480500330354427</v>
       </c>
       <c r="U71">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V71">
         <v>0.29</v>
       </c>
       <c r="W71">
-        <v>0.051049</v>
+        <v>0.053818</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y71">
-        <v>2.500032779294758</v>
+        <v>2.337525936931629</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7414,22 +7414,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1240350884722975</v>
+        <v>0.123851021023653</v>
       </c>
       <c r="C72">
-        <v>576.591878142623</v>
+        <v>567.5825266368346</v>
       </c>
       <c r="D72">
-        <v>1420.791878142623</v>
+        <v>1424.142526636835</v>
       </c>
       <c r="E72">
-        <v>851.1</v>
+        <v>863.46</v>
       </c>
       <c r="F72">
-        <v>865.2</v>
+        <v>877.5600000000001</v>
       </c>
       <c r="G72">
         <v>21</v>
@@ -7450,28 +7450,28 @@
         <v>153.3</v>
       </c>
       <c r="M72">
-        <v>65.58216</v>
+        <v>66.51904800000001</v>
       </c>
       <c r="N72">
-        <v>87.71784000000001</v>
+        <v>86.780952</v>
       </c>
       <c r="O72">
-        <v>25.4381736</v>
+        <v>25.16647608</v>
       </c>
       <c r="P72">
-        <v>62.27966640000001</v>
+        <v>61.61447592</v>
       </c>
       <c r="Q72">
-        <v>67.57966639999999</v>
+        <v>66.91447591999999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.287874961574325</v>
+        <v>0.295311175943631</v>
       </c>
       <c r="T72">
-        <v>1.480500330354427</v>
+        <v>1.525979291742029</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7488,7 +7488,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.337525936931629</v>
+        <v>2.304603036411465</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7496,22 +7496,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.123851021023653</v>
+        <v>0.1236669535750085</v>
       </c>
       <c r="C73">
-        <v>567.582526636834</v>
+        <v>558.589016133969</v>
       </c>
       <c r="D73">
-        <v>1424.142526636834</v>
+        <v>1427.509016133969</v>
       </c>
       <c r="E73">
-        <v>863.4599999999999</v>
+        <v>875.8199999999999</v>
       </c>
       <c r="F73">
-        <v>877.5599999999999</v>
+        <v>889.92</v>
       </c>
       <c r="G73">
         <v>21</v>
@@ -7532,28 +7532,28 @@
         <v>153.3</v>
       </c>
       <c r="M73">
-        <v>66.519048</v>
+        <v>67.45593600000001</v>
       </c>
       <c r="N73">
-        <v>86.78095200000001</v>
+        <v>85.844064</v>
       </c>
       <c r="O73">
-        <v>25.16647608</v>
+        <v>24.89477856</v>
       </c>
       <c r="P73">
-        <v>61.61447592000001</v>
+        <v>60.94928544</v>
       </c>
       <c r="Q73">
-        <v>66.91447592</v>
+        <v>66.24928543999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.295311175943631</v>
+        <v>0.3032785484821732</v>
       </c>
       <c r="T73">
-        <v>1.525979291742028</v>
+        <v>1.574706750371602</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7570,7 +7570,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.304603036411465</v>
+        <v>2.27259466090575</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7578,22 +7578,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1236669535750085</v>
+        <v>0.123482886126364</v>
       </c>
       <c r="C74">
-        <v>558.589016133969</v>
+        <v>549.6114592384827</v>
       </c>
       <c r="D74">
-        <v>1427.509016133969</v>
+        <v>1430.891459238483</v>
       </c>
       <c r="E74">
-        <v>875.8199999999999</v>
+        <v>888.1799999999999</v>
       </c>
       <c r="F74">
-        <v>889.92</v>
+        <v>902.28</v>
       </c>
       <c r="G74">
         <v>21</v>
@@ -7614,28 +7614,28 @@
         <v>153.3</v>
       </c>
       <c r="M74">
-        <v>67.45593600000001</v>
+        <v>68.392824</v>
       </c>
       <c r="N74">
-        <v>85.844064</v>
+        <v>84.90717600000001</v>
       </c>
       <c r="O74">
-        <v>24.89477856</v>
+        <v>24.62308104</v>
       </c>
       <c r="P74">
-        <v>60.94928544</v>
+        <v>60.28409496</v>
       </c>
       <c r="Q74">
-        <v>66.24928543999999</v>
+        <v>65.58409495999999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3032785484821732</v>
+        <v>0.3118360967643111</v>
       </c>
       <c r="T74">
-        <v>1.574706750371602</v>
+        <v>1.627043650381143</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7652,7 +7652,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.27259466090575</v>
+        <v>2.241463227194713</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7660,22 +7660,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.123482886126364</v>
+        <v>0.1232988186777195</v>
       </c>
       <c r="C75">
-        <v>549.6114592384827</v>
+        <v>540.649969624615</v>
       </c>
       <c r="D75">
-        <v>1430.891459238483</v>
+        <v>1434.289969624615</v>
       </c>
       <c r="E75">
-        <v>888.1799999999999</v>
+        <v>900.54</v>
       </c>
       <c r="F75">
-        <v>902.28</v>
+        <v>914.64</v>
       </c>
       <c r="G75">
         <v>21</v>
@@ -7696,28 +7696,28 @@
         <v>153.3</v>
       </c>
       <c r="M75">
-        <v>68.392824</v>
+        <v>69.329712</v>
       </c>
       <c r="N75">
-        <v>84.90717600000001</v>
+        <v>83.97028800000001</v>
       </c>
       <c r="O75">
-        <v>24.62308104</v>
+        <v>24.35138352</v>
       </c>
       <c r="P75">
-        <v>60.28409496</v>
+        <v>59.61890448000001</v>
       </c>
       <c r="Q75">
-        <v>65.58409495999999</v>
+        <v>64.91890447999999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3118360967643111</v>
+        <v>0.3210519179912288</v>
       </c>
       <c r="T75">
-        <v>1.627043650381143</v>
+        <v>1.683406465776035</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7734,7 +7734,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.241463227194713</v>
+        <v>2.211173183583973</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7742,22 +7742,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1232988186777195</v>
+        <v>0.123114751229075</v>
       </c>
       <c r="C76">
-        <v>540.649969624615</v>
+        <v>531.7046620491294</v>
       </c>
       <c r="D76">
-        <v>1434.289969624615</v>
+        <v>1437.704662049129</v>
       </c>
       <c r="E76">
-        <v>900.54</v>
+        <v>912.9</v>
       </c>
       <c r="F76">
-        <v>914.64</v>
+        <v>927</v>
       </c>
       <c r="G76">
         <v>21</v>
@@ -7778,28 +7778,28 @@
         <v>153.3</v>
       </c>
       <c r="M76">
-        <v>69.329712</v>
+        <v>70.26660000000001</v>
       </c>
       <c r="N76">
-        <v>83.97028800000001</v>
+        <v>83.0334</v>
       </c>
       <c r="O76">
-        <v>24.35138352</v>
+        <v>24.079686</v>
       </c>
       <c r="P76">
-        <v>59.61890448000001</v>
+        <v>58.95371400000001</v>
       </c>
       <c r="Q76">
-        <v>64.91890447999999</v>
+        <v>64.25371399999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3210519179912288</v>
+        <v>0.3310050049163001</v>
       </c>
       <c r="T76">
-        <v>1.683406465776035</v>
+        <v>1.744278306402517</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7816,7 +7816,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.211173183583973</v>
+        <v>2.18169087446952</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7824,22 +7824,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.123114751229075</v>
+        <v>0.1229306837804305</v>
       </c>
       <c r="C77">
-        <v>531.7046620491294</v>
+        <v>522.7756523642298</v>
       </c>
       <c r="D77">
-        <v>1437.704662049129</v>
+        <v>1441.13565236423</v>
       </c>
       <c r="E77">
-        <v>912.9</v>
+        <v>925.26</v>
       </c>
       <c r="F77">
-        <v>927</v>
+        <v>939.36</v>
       </c>
       <c r="G77">
         <v>21</v>
@@ -7860,28 +7860,28 @@
         <v>153.3</v>
       </c>
       <c r="M77">
-        <v>70.26660000000001</v>
+        <v>71.20348800000001</v>
       </c>
       <c r="N77">
-        <v>83.0334</v>
+        <v>82.096512</v>
       </c>
       <c r="O77">
-        <v>24.079686</v>
+        <v>23.80798848</v>
       </c>
       <c r="P77">
-        <v>58.95371400000001</v>
+        <v>58.28852352000001</v>
       </c>
       <c r="Q77">
-        <v>64.25371399999999</v>
+        <v>63.58852351999999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3310050049163001</v>
+        <v>0.3417875157517938</v>
       </c>
       <c r="T77">
-        <v>1.744278306402517</v>
+        <v>1.81022280041454</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7898,7 +7898,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.18169087446952</v>
+        <v>2.152984415594921</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7906,22 +7906,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1229306837804305</v>
+        <v>0.122746616331786</v>
       </c>
       <c r="C78">
-        <v>522.7756523642298</v>
+        <v>513.863057530657</v>
       </c>
       <c r="D78">
-        <v>1441.13565236423</v>
+        <v>1444.583057530657</v>
       </c>
       <c r="E78">
-        <v>925.26</v>
+        <v>937.62</v>
       </c>
       <c r="F78">
-        <v>939.36</v>
+        <v>951.72</v>
       </c>
       <c r="G78">
         <v>21</v>
@@ -7942,28 +7942,28 @@
         <v>153.3</v>
       </c>
       <c r="M78">
-        <v>71.20348800000001</v>
+        <v>72.140376</v>
       </c>
       <c r="N78">
-        <v>82.096512</v>
+        <v>81.15962400000001</v>
       </c>
       <c r="O78">
-        <v>23.80798848</v>
+        <v>23.53629096</v>
       </c>
       <c r="P78">
-        <v>58.28852352000001</v>
+        <v>57.62333304000001</v>
       </c>
       <c r="Q78">
-        <v>63.58852351999999</v>
+        <v>62.92333303999999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3417875157517938</v>
+        <v>0.3535076362251566</v>
       </c>
       <c r="T78">
-        <v>1.81022280041454</v>
+        <v>1.881901598253695</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -7980,7 +7980,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.152984415594921</v>
+        <v>2.125023579028753</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7988,22 +7988,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.122746616331786</v>
+        <v>0.1225625488831415</v>
       </c>
       <c r="C79">
-        <v>513.863057530657</v>
+        <v>504.9669956309864</v>
       </c>
       <c r="D79">
-        <v>1444.583057530657</v>
+        <v>1448.046995630986</v>
       </c>
       <c r="E79">
-        <v>937.62</v>
+        <v>949.98</v>
       </c>
       <c r="F79">
-        <v>951.72</v>
+        <v>964.08</v>
       </c>
       <c r="G79">
         <v>21</v>
@@ -8024,28 +8024,28 @@
         <v>153.3</v>
       </c>
       <c r="M79">
-        <v>72.140376</v>
+        <v>73.07726400000001</v>
       </c>
       <c r="N79">
-        <v>81.15962400000001</v>
+        <v>80.222736</v>
       </c>
       <c r="O79">
-        <v>23.53629096</v>
+        <v>23.26459344</v>
       </c>
       <c r="P79">
-        <v>57.62333304000001</v>
+        <v>56.95814256</v>
       </c>
       <c r="Q79">
-        <v>62.92333303999999</v>
+        <v>62.25814255999998</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3535076362251566</v>
+        <v>0.3662932221960979</v>
       </c>
       <c r="T79">
-        <v>1.881901598253695</v>
+        <v>1.960096650441865</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -8062,7 +8062,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.125023579028753</v>
+        <v>2.097779686989923</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8070,22 +8070,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1225625488831415</v>
+        <v>0.122378481434497</v>
       </c>
       <c r="C80">
-        <v>504.9669956309864</v>
+        <v>496.0875858831075</v>
       </c>
       <c r="D80">
-        <v>1448.046995630986</v>
+        <v>1451.527585883108</v>
       </c>
       <c r="E80">
-        <v>949.98</v>
+        <v>962.34</v>
       </c>
       <c r="F80">
-        <v>964.08</v>
+        <v>976.4400000000001</v>
       </c>
       <c r="G80">
         <v>21</v>
@@ -8106,28 +8106,28 @@
         <v>153.3</v>
       </c>
       <c r="M80">
-        <v>73.07726400000001</v>
+        <v>74.01415200000001</v>
       </c>
       <c r="N80">
-        <v>80.222736</v>
+        <v>79.285848</v>
       </c>
       <c r="O80">
-        <v>23.26459344</v>
+        <v>22.99289592</v>
       </c>
       <c r="P80">
-        <v>56.95814256</v>
+        <v>56.29295208000001</v>
       </c>
       <c r="Q80">
-        <v>62.25814255999998</v>
+        <v>61.59295207999999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3662932221960979</v>
+        <v>0.3802964830214145</v>
       </c>
       <c r="T80">
-        <v>1.960096650441865</v>
+        <v>2.045738850457479</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -8144,7 +8144,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.097779686989923</v>
+        <v>2.071225513736886</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8152,22 +8152,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.122378481434497</v>
+        <v>0.1221944139858525</v>
       </c>
       <c r="C81">
-        <v>496.0875858831075</v>
+        <v>487.2249486538998</v>
       </c>
       <c r="D81">
-        <v>1451.527585883108</v>
+        <v>1455.0249486539</v>
       </c>
       <c r="E81">
-        <v>962.34</v>
+        <v>974.7</v>
       </c>
       <c r="F81">
-        <v>976.4400000000001</v>
+        <v>988.8000000000001</v>
       </c>
       <c r="G81">
         <v>21</v>
@@ -8188,28 +8188,28 @@
         <v>153.3</v>
       </c>
       <c r="M81">
-        <v>74.01415200000001</v>
+        <v>74.95104000000001</v>
       </c>
       <c r="N81">
-        <v>79.285848</v>
+        <v>78.34896000000001</v>
       </c>
       <c r="O81">
-        <v>22.99289592</v>
+        <v>22.7211984</v>
       </c>
       <c r="P81">
-        <v>56.29295208000001</v>
+        <v>55.62776160000001</v>
       </c>
       <c r="Q81">
-        <v>61.59295207999999</v>
+        <v>60.92776159999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3802964830214145</v>
+        <v>0.3957000699292627</v>
       </c>
       <c r="T81">
-        <v>2.045738850457479</v>
+        <v>2.139945270474654</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -8226,7 +8226,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.071225513736886</v>
+        <v>2.045335194815175</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8234,22 +8234,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1221944139858525</v>
+        <v>0.122010346537208</v>
       </c>
       <c r="C82">
-        <v>487.2249486538998</v>
+        <v>478.3792054731102</v>
       </c>
       <c r="D82">
-        <v>1455.0249486539</v>
+        <v>1458.53920547311</v>
       </c>
       <c r="E82">
-        <v>974.7</v>
+        <v>987.0600000000001</v>
       </c>
       <c r="F82">
-        <v>988.8000000000001</v>
+        <v>1001.16</v>
       </c>
       <c r="G82">
         <v>21</v>
@@ -8270,28 +8270,28 @@
         <v>153.3</v>
       </c>
       <c r="M82">
-        <v>74.95104000000001</v>
+        <v>75.88792800000002</v>
       </c>
       <c r="N82">
-        <v>78.34896000000001</v>
+        <v>77.41207199999999</v>
       </c>
       <c r="O82">
-        <v>22.7211984</v>
+        <v>22.44950088</v>
       </c>
       <c r="P82">
-        <v>55.62776160000001</v>
+        <v>54.96257111999999</v>
       </c>
       <c r="Q82">
-        <v>60.92776159999999</v>
+        <v>60.26257111999998</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3957000699292627</v>
+        <v>0.4127250870379371</v>
       </c>
       <c r="T82">
-        <v>2.139945270474654</v>
+        <v>2.244068155756795</v>
       </c>
       <c r="U82">
         <v>0.07580000000000001</v>
@@ -8308,7 +8308,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.045335194815175</v>
+        <v>2.020084143027333</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8316,22 +8316,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.122010346537208</v>
+        <v>0.1300935190885635</v>
       </c>
       <c r="C83">
-        <v>478.3792054731102</v>
+        <v>326.1552610295377</v>
       </c>
       <c r="D83">
-        <v>1458.53920547311</v>
+        <v>1318.675261029538</v>
       </c>
       <c r="E83">
-        <v>987.0600000000001</v>
+        <v>999.4200000000001</v>
       </c>
       <c r="F83">
-        <v>1001.16</v>
+        <v>1013.52</v>
       </c>
       <c r="G83">
         <v>21</v>
@@ -8352,45 +8352,45 @@
         <v>153.3</v>
       </c>
       <c r="M83">
-        <v>75.88792800000002</v>
+        <v>91.21680000000001</v>
       </c>
       <c r="N83">
-        <v>77.41207199999999</v>
+        <v>62.08320000000001</v>
       </c>
       <c r="O83">
-        <v>22.44950088</v>
+        <v>18.004128</v>
       </c>
       <c r="P83">
-        <v>54.96257111999999</v>
+        <v>44.079072</v>
       </c>
       <c r="Q83">
-        <v>60.26257111999998</v>
+        <v>49.37907199999999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4127250870379371</v>
+        <v>0.431641772714242</v>
       </c>
       <c r="T83">
-        <v>2.244068155756795</v>
+        <v>2.35976025051473</v>
       </c>
       <c r="U83">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V83">
         <v>0.29</v>
       </c>
       <c r="W83">
-        <v>0.053818</v>
+        <v>0.0639</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y83">
-        <v>2.020084143027333</v>
+        <v>1.680611466308838</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8398,22 +8398,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1300935190885635</v>
+        <v>0.130010271639919</v>
       </c>
       <c r="C84">
-        <v>326.1552610295377</v>
+        <v>315.0988591409503</v>
       </c>
       <c r="D84">
-        <v>1318.675261029538</v>
+        <v>1319.97885914095</v>
       </c>
       <c r="E84">
-        <v>999.4200000000001</v>
+        <v>1011.78</v>
       </c>
       <c r="F84">
-        <v>1013.52</v>
+        <v>1025.88</v>
       </c>
       <c r="G84">
         <v>21</v>
@@ -8434,28 +8434,28 @@
         <v>153.3</v>
       </c>
       <c r="M84">
-        <v>91.21680000000001</v>
+        <v>92.3292</v>
       </c>
       <c r="N84">
-        <v>62.08320000000001</v>
+        <v>60.97080000000001</v>
       </c>
       <c r="O84">
-        <v>18.004128</v>
+        <v>17.681532</v>
       </c>
       <c r="P84">
-        <v>44.079072</v>
+        <v>43.28926800000001</v>
       </c>
       <c r="Q84">
-        <v>49.37907199999999</v>
+        <v>48.58926799999999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.431641772714242</v>
+        <v>0.4527839508230533</v>
       </c>
       <c r="T84">
-        <v>2.35976025051473</v>
+        <v>2.489063179950069</v>
       </c>
       <c r="U84">
         <v>0.09</v>
@@ -8472,7 +8472,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.680611466308838</v>
+        <v>1.660363135389454</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8480,22 +8480,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.130010271639919</v>
+        <v>0.1299270241912746</v>
       </c>
       <c r="C85">
-        <v>315.0988591409503</v>
+        <v>304.045037189496</v>
       </c>
       <c r="D85">
-        <v>1319.97885914095</v>
+        <v>1321.285037189496</v>
       </c>
       <c r="E85">
-        <v>1011.78</v>
+        <v>1024.14</v>
       </c>
       <c r="F85">
-        <v>1025.88</v>
+        <v>1038.24</v>
       </c>
       <c r="G85">
         <v>21</v>
@@ -8516,28 +8516,28 @@
         <v>153.3</v>
       </c>
       <c r="M85">
-        <v>92.3292</v>
+        <v>93.44159999999999</v>
       </c>
       <c r="N85">
-        <v>60.97080000000001</v>
+        <v>59.85840000000002</v>
       </c>
       <c r="O85">
-        <v>17.681532</v>
+        <v>17.358936</v>
       </c>
       <c r="P85">
-        <v>43.28926800000001</v>
+        <v>42.49946400000002</v>
       </c>
       <c r="Q85">
-        <v>48.58926799999999</v>
+        <v>47.799464</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4527839508230533</v>
+        <v>0.4765689011954662</v>
       </c>
       <c r="T85">
-        <v>2.489063179950069</v>
+        <v>2.634528975564826</v>
       </c>
       <c r="U85">
         <v>0.09</v>
@@ -8554,7 +8554,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.660363135389454</v>
+        <v>1.640596907587199</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8562,22 +8562,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1299270241912746</v>
+        <v>0.1298437767426301</v>
       </c>
       <c r="C86">
-        <v>304.045037189496</v>
+        <v>292.9938028416516</v>
       </c>
       <c r="D86">
-        <v>1321.285037189496</v>
+        <v>1322.593802841651</v>
       </c>
       <c r="E86">
-        <v>1024.14</v>
+        <v>1036.5</v>
       </c>
       <c r="F86">
-        <v>1038.24</v>
+        <v>1050.6</v>
       </c>
       <c r="G86">
         <v>21</v>
@@ -8598,28 +8598,28 @@
         <v>153.3</v>
       </c>
       <c r="M86">
-        <v>93.44159999999999</v>
+        <v>94.55399999999999</v>
       </c>
       <c r="N86">
-        <v>59.85840000000002</v>
+        <v>58.74600000000002</v>
       </c>
       <c r="O86">
-        <v>17.358936</v>
+        <v>17.03634000000001</v>
       </c>
       <c r="P86">
-        <v>42.49946400000002</v>
+        <v>41.70966000000001</v>
       </c>
       <c r="Q86">
-        <v>47.799464</v>
+        <v>47.00966</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4765689011954659</v>
+        <v>0.5035251782842003</v>
       </c>
       <c r="T86">
-        <v>2.634528975564824</v>
+        <v>2.799390210594881</v>
       </c>
       <c r="U86">
         <v>0.09</v>
@@ -8636,7 +8636,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.640596907587199</v>
+        <v>1.621295767497938</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8644,22 +8644,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1298437767426301</v>
+        <v>0.1297605292939856</v>
       </c>
       <c r="C87">
-        <v>292.9938028416516</v>
+        <v>281.9451637942968</v>
       </c>
       <c r="D87">
-        <v>1322.593802841651</v>
+        <v>1323.905163794297</v>
       </c>
       <c r="E87">
-        <v>1036.5</v>
+        <v>1048.86</v>
       </c>
       <c r="F87">
-        <v>1050.6</v>
+        <v>1062.96</v>
       </c>
       <c r="G87">
         <v>21</v>
@@ -8680,28 +8680,28 @@
         <v>153.3</v>
       </c>
       <c r="M87">
-        <v>94.55399999999999</v>
+        <v>95.6664</v>
       </c>
       <c r="N87">
-        <v>58.74600000000002</v>
+        <v>57.63360000000002</v>
       </c>
       <c r="O87">
-        <v>17.03634000000001</v>
+        <v>16.713744</v>
       </c>
       <c r="P87">
-        <v>41.70966000000001</v>
+        <v>40.91985600000001</v>
       </c>
       <c r="Q87">
-        <v>47.00966</v>
+        <v>46.21985599999999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.5035251782842003</v>
+        <v>0.5343323520998968</v>
       </c>
       <c r="T87">
-        <v>2.799390210594881</v>
+        <v>2.987803050629232</v>
       </c>
       <c r="U87">
         <v>0.09</v>
@@ -8718,7 +8718,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>1.621295767497938</v>
+        <v>1.602443491131683</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8726,22 +8726,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1297605292939856</v>
+        <v>0.1296772818453411</v>
       </c>
       <c r="C88">
-        <v>281.9451637942968</v>
+        <v>270.8991277748703</v>
       </c>
       <c r="D88">
-        <v>1323.905163794297</v>
+        <v>1325.21912777487</v>
       </c>
       <c r="E88">
-        <v>1048.86</v>
+        <v>1061.22</v>
       </c>
       <c r="F88">
-        <v>1062.96</v>
+        <v>1075.32</v>
       </c>
       <c r="G88">
         <v>21</v>
@@ -8762,28 +8762,28 @@
         <v>153.3</v>
       </c>
       <c r="M88">
-        <v>95.6664</v>
+        <v>96.77879999999999</v>
       </c>
       <c r="N88">
-        <v>57.63360000000002</v>
+        <v>56.52120000000002</v>
       </c>
       <c r="O88">
-        <v>16.713744</v>
+        <v>16.391148</v>
       </c>
       <c r="P88">
-        <v>40.91985600000001</v>
+        <v>40.13005200000002</v>
       </c>
       <c r="Q88">
-        <v>46.21985599999999</v>
+        <v>45.430052</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5343323520998968</v>
+        <v>0.5698790911180081</v>
       </c>
       <c r="T88">
-        <v>2.987803050629232</v>
+        <v>3.205202481438098</v>
       </c>
       <c r="U88">
         <v>0.09</v>
@@ -8800,7 +8800,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.602443491131683</v>
+        <v>1.58402460042902</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8808,22 +8808,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1296772818453411</v>
+        <v>0.1295940343966966</v>
       </c>
       <c r="C89">
-        <v>270.8991277748703</v>
+        <v>259.8557025415162</v>
       </c>
       <c r="D89">
-        <v>1325.21912777487</v>
+        <v>1326.535702541516</v>
       </c>
       <c r="E89">
-        <v>1061.22</v>
+        <v>1073.58</v>
       </c>
       <c r="F89">
-        <v>1075.32</v>
+        <v>1087.68</v>
       </c>
       <c r="G89">
         <v>21</v>
@@ -8844,28 +8844,28 @@
         <v>153.3</v>
       </c>
       <c r="M89">
-        <v>96.77879999999999</v>
+        <v>97.8912</v>
       </c>
       <c r="N89">
-        <v>56.52120000000002</v>
+        <v>55.40880000000001</v>
       </c>
       <c r="O89">
-        <v>16.391148</v>
+        <v>16.068552</v>
       </c>
       <c r="P89">
-        <v>40.13005200000002</v>
+        <v>39.34024800000001</v>
       </c>
       <c r="Q89">
-        <v>45.430052</v>
+        <v>44.64024799999999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5698790911180081</v>
+        <v>0.611350286639138</v>
       </c>
       <c r="T89">
-        <v>3.205202481438098</v>
+        <v>3.458835150715109</v>
       </c>
       <c r="U89">
         <v>0.09</v>
@@ -8882,7 +8882,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>1.58402460042902</v>
+        <v>1.56602432087869</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8890,22 +8890,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1295940343966966</v>
+        <v>0.1295107869480521</v>
       </c>
       <c r="C90">
-        <v>259.8557025415162</v>
+        <v>248.814895883241</v>
       </c>
       <c r="D90">
-        <v>1326.535702541516</v>
+        <v>1327.854895883241</v>
       </c>
       <c r="E90">
-        <v>1073.58</v>
+        <v>1085.94</v>
       </c>
       <c r="F90">
-        <v>1087.68</v>
+        <v>1100.04</v>
       </c>
       <c r="G90">
         <v>21</v>
@@ -8926,28 +8926,28 @@
         <v>153.3</v>
       </c>
       <c r="M90">
-        <v>97.8912</v>
+        <v>99.00359999999999</v>
       </c>
       <c r="N90">
-        <v>55.40880000000001</v>
+        <v>54.29640000000002</v>
       </c>
       <c r="O90">
-        <v>16.068552</v>
+        <v>15.745956</v>
       </c>
       <c r="P90">
-        <v>39.34024800000001</v>
+        <v>38.55044400000001</v>
       </c>
       <c r="Q90">
-        <v>44.64024799999999</v>
+        <v>43.850444</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.611350286639138</v>
+        <v>0.6603616995277461</v>
       </c>
       <c r="T90">
-        <v>3.458835150715109</v>
+        <v>3.758582850769758</v>
       </c>
       <c r="U90">
         <v>0.09</v>
@@ -8964,7 +8964,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>1.56602432087869</v>
+        <v>1.548428541992413</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8972,22 +8972,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1295107869480521</v>
+        <v>0.1294275394994076</v>
       </c>
       <c r="C91">
-        <v>248.814895883241</v>
+        <v>237.7767156200653</v>
       </c>
       <c r="D91">
-        <v>1327.854895883241</v>
+        <v>1329.176715620065</v>
       </c>
       <c r="E91">
-        <v>1085.94</v>
+        <v>1098.3</v>
       </c>
       <c r="F91">
-        <v>1100.04</v>
+        <v>1112.4</v>
       </c>
       <c r="G91">
         <v>21</v>
@@ -9008,28 +9008,28 @@
         <v>153.3</v>
       </c>
       <c r="M91">
-        <v>99.00359999999999</v>
+        <v>100.116</v>
       </c>
       <c r="N91">
-        <v>54.29640000000002</v>
+        <v>53.18400000000001</v>
       </c>
       <c r="O91">
-        <v>15.745956</v>
+        <v>15.42336</v>
       </c>
       <c r="P91">
-        <v>38.55044400000001</v>
+        <v>37.76064000000001</v>
       </c>
       <c r="Q91">
-        <v>43.850444</v>
+        <v>43.06063999999999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6603616995277461</v>
+        <v>0.7191753949940759</v>
       </c>
       <c r="T91">
-        <v>3.758582850769758</v>
+        <v>4.118280090835337</v>
       </c>
       <c r="U91">
         <v>0.09</v>
@@ -9046,7 +9046,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>1.548428541992413</v>
+        <v>1.531223780414719</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9054,22 +9054,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1294275394994076</v>
+        <v>0.1293442920507631</v>
       </c>
       <c r="C92">
-        <v>237.7767156200653</v>
+        <v>226.7411696031786</v>
       </c>
       <c r="D92">
-        <v>1329.176715620065</v>
+        <v>1330.501169603179</v>
       </c>
       <c r="E92">
-        <v>1098.3</v>
+        <v>1110.66</v>
       </c>
       <c r="F92">
-        <v>1112.4</v>
+        <v>1124.76</v>
       </c>
       <c r="G92">
         <v>21</v>
@@ -9090,28 +9090,28 @@
         <v>153.3</v>
       </c>
       <c r="M92">
-        <v>100.116</v>
+        <v>101.2284</v>
       </c>
       <c r="N92">
-        <v>53.18400000000001</v>
+        <v>52.07160000000002</v>
       </c>
       <c r="O92">
-        <v>15.42336</v>
+        <v>15.100764</v>
       </c>
       <c r="P92">
-        <v>37.76064000000001</v>
+        <v>36.97083600000001</v>
       </c>
       <c r="Q92">
-        <v>43.06063999999999</v>
+        <v>42.270836</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.7191753949940759</v>
+        <v>0.7910588005640347</v>
       </c>
       <c r="T92">
-        <v>4.118280090835337</v>
+        <v>4.55791005091549</v>
       </c>
       <c r="U92">
         <v>0.09</v>
@@ -9128,7 +9128,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>1.531223780414719</v>
+        <v>1.514397145465107</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9136,22 +9136,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1293442920507631</v>
+        <v>0.1715454912321817</v>
       </c>
       <c r="C93">
-        <v>226.7411696031786</v>
+        <v>-232.1457342192322</v>
       </c>
       <c r="D93">
-        <v>1330.501169603179</v>
+        <v>883.974265780768</v>
       </c>
       <c r="E93">
-        <v>1110.66</v>
+        <v>1123.02</v>
       </c>
       <c r="F93">
-        <v>1124.76</v>
+        <v>1137.12</v>
       </c>
       <c r="G93">
         <v>21</v>
@@ -9172,45 +9172,45 @@
         <v>153.3</v>
       </c>
       <c r="M93">
-        <v>101.2284</v>
+        <v>166.929216</v>
       </c>
       <c r="N93">
-        <v>52.07160000000002</v>
+        <v>-13.62921600000001</v>
       </c>
       <c r="O93">
-        <v>15.100764</v>
+        <v>-3.952472640000004</v>
       </c>
       <c r="P93">
-        <v>36.97083600000001</v>
+        <v>-9.67674336000001</v>
       </c>
       <c r="Q93">
-        <v>42.270836</v>
+        <v>-4.376743360000027</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7910588005640347</v>
+        <v>0.9057242229265435</v>
       </c>
       <c r="T93">
-        <v>4.55791005091549</v>
+        <v>5.259189499991439</v>
       </c>
       <c r="U93">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.29</v>
+        <v>0.2663224632888709</v>
       </c>
       <c r="W93">
-        <v>0.0639</v>
+        <v>0.1077038623891938</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y93">
-        <v>1.514397145465107</v>
+        <v>0.9183533216857617</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9218,22 +9218,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1715454912321817</v>
+        <v>0.1725554912321817</v>
       </c>
       <c r="C94">
-        <v>-232.1457342192322</v>
+        <v>-251.5493265698244</v>
       </c>
       <c r="D94">
-        <v>883.974265780768</v>
+        <v>876.9306734301756</v>
       </c>
       <c r="E94">
-        <v>1123.02</v>
+        <v>1135.38</v>
       </c>
       <c r="F94">
-        <v>1137.12</v>
+        <v>1149.48</v>
       </c>
       <c r="G94">
         <v>21</v>
@@ -9254,37 +9254,37 @@
         <v>153.3</v>
       </c>
       <c r="M94">
-        <v>166.929216</v>
+        <v>168.743664</v>
       </c>
       <c r="N94">
-        <v>-13.62921600000001</v>
+        <v>-15.44366400000001</v>
       </c>
       <c r="O94">
-        <v>-3.952472640000004</v>
+        <v>-4.478662560000004</v>
       </c>
       <c r="P94">
-        <v>-9.67674336000001</v>
+        <v>-10.96500144000001</v>
       </c>
       <c r="Q94">
-        <v>-4.376743360000027</v>
+        <v>-5.665001440000026</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.9057242229265435</v>
+        <v>1.028570540487479</v>
       </c>
       <c r="T94">
-        <v>5.259189499991439</v>
+        <v>6.010502285704503</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.2663224632888709</v>
+        <v>0.2634587808879152</v>
       </c>
       <c r="W94">
-        <v>0.1077038623891938</v>
+        <v>0.1081242509656541</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.9183533216857617</v>
+        <v>0.9084785547859148</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9300,22 +9300,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1725554912321817</v>
+        <v>0.1735654912321817</v>
       </c>
       <c r="C95">
-        <v>-251.5493265698244</v>
+        <v>-270.8415582046949</v>
       </c>
       <c r="D95">
-        <v>876.9306734301756</v>
+        <v>869.9984417953052</v>
       </c>
       <c r="E95">
-        <v>1135.38</v>
+        <v>1147.74</v>
       </c>
       <c r="F95">
-        <v>1149.48</v>
+        <v>1161.84</v>
       </c>
       <c r="G95">
         <v>21</v>
@@ -9336,37 +9336,37 @@
         <v>153.3</v>
       </c>
       <c r="M95">
-        <v>168.743664</v>
+        <v>170.5581120000001</v>
       </c>
       <c r="N95">
-        <v>-15.44366400000001</v>
+        <v>-17.25811200000004</v>
       </c>
       <c r="O95">
-        <v>-4.478662560000004</v>
+        <v>-5.004852480000011</v>
       </c>
       <c r="P95">
-        <v>-10.96500144000001</v>
+        <v>-12.25325952000003</v>
       </c>
       <c r="Q95">
-        <v>-5.665001440000026</v>
+        <v>-6.953259520000046</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.028570540487479</v>
+        <v>1.192365630568725</v>
       </c>
       <c r="T95">
-        <v>6.010502285704503</v>
+        <v>7.012252666655256</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.2634587808879152</v>
+        <v>0.2606560278997459</v>
       </c>
       <c r="W95">
-        <v>0.1081242509656541</v>
+        <v>0.1085356951043173</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9374,7 +9374,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.9084785547859148</v>
+        <v>0.8988138893094687</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9382,22 +9382,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1735654912321817</v>
+        <v>0.1745754912321817</v>
       </c>
       <c r="C96">
-        <v>-270.8415582046949</v>
+        <v>-290.0250493659822</v>
       </c>
       <c r="D96">
-        <v>869.9984417953052</v>
+        <v>863.1749506340178</v>
       </c>
       <c r="E96">
-        <v>1147.74</v>
+        <v>1160.1</v>
       </c>
       <c r="F96">
-        <v>1161.84</v>
+        <v>1174.2</v>
       </c>
       <c r="G96">
         <v>21</v>
@@ -9418,37 +9418,37 @@
         <v>153.3</v>
       </c>
       <c r="M96">
-        <v>170.5581120000001</v>
+        <v>172.37256</v>
       </c>
       <c r="N96">
-        <v>-17.25811200000004</v>
+        <v>-19.07256000000001</v>
       </c>
       <c r="O96">
-        <v>-5.004852480000011</v>
+        <v>-5.531042400000002</v>
       </c>
       <c r="P96">
-        <v>-12.25325952000003</v>
+        <v>-13.54151760000001</v>
       </c>
       <c r="Q96">
-        <v>-6.953259520000046</v>
+        <v>-8.241517600000025</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.192365630568725</v>
+        <v>1.421678756682471</v>
       </c>
       <c r="T96">
-        <v>7.012252666655256</v>
+        <v>8.41470319998631</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.2606560278997459</v>
+        <v>0.2579122802376434</v>
       </c>
       <c r="W96">
-        <v>0.1085356951043173</v>
+        <v>0.108938477261114</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9456,7 +9456,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8988138893094687</v>
+        <v>0.8893526904746324</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9464,22 +9464,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1745754912321817</v>
+        <v>0.1755854912321818</v>
       </c>
       <c r="C97">
-        <v>-290.0250493659822</v>
+        <v>-309.1023387321779</v>
       </c>
       <c r="D97">
-        <v>863.1749506340178</v>
+        <v>856.4576612678222</v>
       </c>
       <c r="E97">
-        <v>1160.1</v>
+        <v>1172.46</v>
       </c>
       <c r="F97">
-        <v>1174.2</v>
+        <v>1186.56</v>
       </c>
       <c r="G97">
         <v>21</v>
@@ -9500,37 +9500,37 @@
         <v>153.3</v>
       </c>
       <c r="M97">
-        <v>172.37256</v>
+        <v>174.187008</v>
       </c>
       <c r="N97">
-        <v>-19.07256000000001</v>
+        <v>-20.88700800000004</v>
       </c>
       <c r="O97">
-        <v>-5.531042400000002</v>
+        <v>-6.05723232000001</v>
       </c>
       <c r="P97">
-        <v>-13.54151760000001</v>
+        <v>-14.82977568000003</v>
       </c>
       <c r="Q97">
-        <v>-8.241517600000025</v>
+        <v>-9.529775680000043</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.421678756682471</v>
+        <v>1.76564844585309</v>
       </c>
       <c r="T97">
-        <v>8.41470319998631</v>
+        <v>10.51837899998289</v>
       </c>
       <c r="U97">
         <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.2579122802376434</v>
+        <v>0.2552256939851679</v>
       </c>
       <c r="W97">
-        <v>0.108938477261114</v>
+        <v>0.1093328681229774</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8893526904746324</v>
+        <v>0.8800885999488548</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9546,22 +9546,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1755854912321817</v>
+        <v>0.1765954912321817</v>
       </c>
       <c r="C98">
-        <v>-309.1023387321774</v>
+        <v>-328.0758865672856</v>
       </c>
       <c r="D98">
-        <v>856.4576612678226</v>
+        <v>849.8441134327145</v>
       </c>
       <c r="E98">
-        <v>1172.46</v>
+        <v>1184.82</v>
       </c>
       <c r="F98">
-        <v>1186.56</v>
+        <v>1198.92</v>
       </c>
       <c r="G98">
         <v>21</v>
@@ -9582,37 +9582,37 @@
         <v>153.3</v>
       </c>
       <c r="M98">
-        <v>174.187008</v>
+        <v>176.001456</v>
       </c>
       <c r="N98">
-        <v>-20.88700800000001</v>
+        <v>-22.70145600000001</v>
       </c>
       <c r="O98">
-        <v>-6.057232320000002</v>
+        <v>-6.583422240000002</v>
       </c>
       <c r="P98">
-        <v>-14.82977568000001</v>
+        <v>-16.11803376000001</v>
       </c>
       <c r="Q98">
-        <v>-9.529775680000023</v>
+        <v>-10.81803376000002</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.765648445853085</v>
+        <v>2.338931261137446</v>
       </c>
       <c r="T98">
-        <v>10.51837899998286</v>
+        <v>14.02450533331049</v>
       </c>
       <c r="U98">
         <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.2552256939851679</v>
+        <v>0.2525945012636713</v>
       </c>
       <c r="W98">
-        <v>0.1093328681229774</v>
+        <v>0.1097191272144931</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9620,7 +9620,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8800885999488549</v>
+        <v>0.8710155215988667</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9628,22 +9628,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1765954912321817</v>
+        <v>0.1776054912321817</v>
       </c>
       <c r="C99">
-        <v>-328.0758865672856</v>
+        <v>-346.9480777252022</v>
       </c>
       <c r="D99">
-        <v>849.8441134327145</v>
+        <v>843.3319222747978</v>
       </c>
       <c r="E99">
-        <v>1184.82</v>
+        <v>1197.18</v>
       </c>
       <c r="F99">
-        <v>1198.92</v>
+        <v>1211.28</v>
       </c>
       <c r="G99">
         <v>21</v>
@@ -9664,37 +9664,37 @@
         <v>153.3</v>
       </c>
       <c r="M99">
-        <v>176.001456</v>
+        <v>177.815904</v>
       </c>
       <c r="N99">
-        <v>-22.70145600000001</v>
+        <v>-24.51590400000001</v>
       </c>
       <c r="O99">
-        <v>-6.583422240000002</v>
+        <v>-7.109612160000001</v>
       </c>
       <c r="P99">
-        <v>-16.11803376000001</v>
+        <v>-17.40629184000001</v>
       </c>
       <c r="Q99">
-        <v>-10.81803376000002</v>
+        <v>-12.10629184000002</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.338931261137446</v>
+        <v>3.485496891706169</v>
       </c>
       <c r="T99">
-        <v>14.02450533331049</v>
+        <v>21.03675799996573</v>
       </c>
       <c r="U99">
         <v>0.1468</v>
       </c>
       <c r="V99">
-        <v>0.2525945012636713</v>
+        <v>0.2500170063528175</v>
       </c>
       <c r="W99">
-        <v>0.1097191272144931</v>
+        <v>0.1100975034674064</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9702,7 +9702,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8710155215988667</v>
+        <v>0.862127608113164</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9710,22 +9710,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1776054912321817</v>
+        <v>0.1786154912321817</v>
       </c>
       <c r="C100">
-        <v>-346.9480777252022</v>
+        <v>-365.7212245170062</v>
       </c>
       <c r="D100">
-        <v>843.3319222747978</v>
+        <v>836.9187754829939</v>
       </c>
       <c r="E100">
-        <v>1197.18</v>
+        <v>1209.54</v>
       </c>
       <c r="F100">
-        <v>1211.28</v>
+        <v>1223.64</v>
       </c>
       <c r="G100">
         <v>21</v>
@@ -9746,37 +9746,37 @@
         <v>153.3</v>
       </c>
       <c r="M100">
-        <v>177.815904</v>
+        <v>179.630352</v>
       </c>
       <c r="N100">
-        <v>-24.51590400000001</v>
+        <v>-26.33035200000003</v>
       </c>
       <c r="O100">
-        <v>-7.109612160000001</v>
+        <v>-7.635802080000009</v>
       </c>
       <c r="P100">
-        <v>-17.40629184000001</v>
+        <v>-18.69454992000002</v>
       </c>
       <c r="Q100">
-        <v>-12.10629184000002</v>
+        <v>-13.39454992000004</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.485496891706169</v>
+        <v>6.925193783412339</v>
       </c>
       <c r="T100">
-        <v>21.03675799996573</v>
+        <v>42.07351599993146</v>
       </c>
       <c r="U100">
         <v>0.1468</v>
       </c>
       <c r="V100">
-        <v>0.2500170063528175</v>
+        <v>0.2474915820462234</v>
       </c>
       <c r="W100">
-        <v>0.1100975034674064</v>
+        <v>0.1104682357556144</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9784,91 +9784,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.862127608113164</v>
+        <v>0.8534192484352532</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1786154912321817</v>
-      </c>
-      <c r="C101">
-        <v>-365.7212245170062</v>
-      </c>
-      <c r="D101">
-        <v>836.9187754829939</v>
-      </c>
-      <c r="E101">
-        <v>1209.54</v>
-      </c>
-      <c r="F101">
-        <v>1223.64</v>
-      </c>
-      <c r="G101">
-        <v>21</v>
-      </c>
-      <c r="H101">
-        <v>1221.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>158.6</v>
-      </c>
-      <c r="K101">
-        <v>5.299999999999983</v>
-      </c>
-      <c r="L101">
-        <v>153.3</v>
-      </c>
-      <c r="M101">
-        <v>179.630352</v>
-      </c>
-      <c r="N101">
-        <v>-26.33035200000003</v>
-      </c>
-      <c r="O101">
-        <v>-7.635802080000009</v>
-      </c>
-      <c r="P101">
-        <v>-18.69454992000002</v>
-      </c>
-      <c r="Q101">
-        <v>-13.39454992000004</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.925193783412339</v>
-      </c>
-      <c r="T101">
-        <v>42.07351599993146</v>
-      </c>
-      <c r="U101">
-        <v>0.1468</v>
-      </c>
-      <c r="V101">
-        <v>0.2474915820462234</v>
-      </c>
-      <c r="W101">
-        <v>0.1104682357556144</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.8534192484352532</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
